--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{275C066A-9190-4350-B06B-120F0771C3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80168593-E798-419B-AAC8-0DE51E7B4C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1132" uniqueCount="297">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -712,15 +712,21 @@
     <t>at grid node - w175406958-220</t>
   </si>
   <si>
-    <t>PL2-220</t>
-  </si>
-  <si>
-    <t>at grid node - PL2-220</t>
+    <t>PL15-400</t>
+  </si>
+  <si>
+    <t>at grid node - PL15-400</t>
   </si>
   <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>PL17-400</t>
+  </si>
+  <si>
+    <t>at grid node - PL17-400</t>
+  </si>
+  <si>
     <t>PL27-400</t>
   </si>
   <si>
@@ -733,10 +739,22 @@
     <t>at grid node - PL32-220</t>
   </si>
   <si>
-    <t>PL37-220</t>
-  </si>
-  <si>
-    <t>at grid node - PL37-220</t>
+    <t>PL34-400</t>
+  </si>
+  <si>
+    <t>at grid node - PL34-400</t>
+  </si>
+  <si>
+    <t>PL36-400</t>
+  </si>
+  <si>
+    <t>at grid node - PL36-400</t>
+  </si>
+  <si>
+    <t>PL51-400</t>
+  </si>
+  <si>
+    <t>at grid node - PL51-400</t>
   </si>
   <si>
     <t>PL55-220</t>
@@ -745,6 +763,12 @@
     <t>at grid node - PL55-220</t>
   </si>
   <si>
+    <t>PL62-400</t>
+  </si>
+  <si>
+    <t>at grid node - PL62-400</t>
+  </si>
+  <si>
     <t>r18085709-400</t>
   </si>
   <si>
@@ -757,28 +781,16 @@
     <t>at grid node - w101915790-220</t>
   </si>
   <si>
-    <t>w102165724-220</t>
-  </si>
-  <si>
-    <t>at grid node - w102165724-220</t>
-  </si>
-  <si>
     <t>w131120723-220</t>
   </si>
   <si>
     <t>at grid node - w131120723-220</t>
   </si>
   <si>
-    <t>w133537926-220</t>
-  </si>
-  <si>
-    <t>at grid node - w133537926-220</t>
-  </si>
-  <si>
-    <t>w139452056-220</t>
-  </si>
-  <si>
-    <t>at grid node - w139452056-220</t>
+    <t>w144646702-400</t>
+  </si>
+  <si>
+    <t>at grid node - w144646702-400</t>
   </si>
   <si>
     <t>w145037309-220</t>
@@ -787,6 +799,12 @@
     <t>at grid node - w145037309-220</t>
   </si>
   <si>
+    <t>w148060965-400</t>
+  </si>
+  <si>
+    <t>at grid node - w148060965-400</t>
+  </si>
+  <si>
     <t>w148197330-220</t>
   </si>
   <si>
@@ -799,10 +817,10 @@
     <t>at grid node - w154894455-400</t>
   </si>
   <si>
-    <t>w170316833-220</t>
-  </si>
-  <si>
-    <t>at grid node - w170316833-220</t>
+    <t>w173582810-400</t>
+  </si>
+  <si>
+    <t>at grid node - w173582810-400</t>
   </si>
   <si>
     <t>w175406958-400</t>
@@ -811,42 +829,42 @@
     <t>at grid node - w175406958-400</t>
   </si>
   <si>
-    <t>w177749653-220</t>
-  </si>
-  <si>
-    <t>at grid node - w177749653-220</t>
-  </si>
-  <si>
-    <t>w178756295-220</t>
-  </si>
-  <si>
-    <t>at grid node - w178756295-220</t>
-  </si>
-  <si>
     <t>w183259405-220</t>
   </si>
   <si>
     <t>at grid node - w183259405-220</t>
   </si>
   <si>
+    <t>w199098050-400</t>
+  </si>
+  <si>
+    <t>at grid node - w199098050-400</t>
+  </si>
+  <si>
+    <t>w215282393-400</t>
+  </si>
+  <si>
+    <t>at grid node - w215282393-400</t>
+  </si>
+  <si>
     <t>w228154083-220</t>
   </si>
   <si>
     <t>at grid node - w228154083-220</t>
   </si>
   <si>
-    <t>w238640596-220</t>
-  </si>
-  <si>
-    <t>at grid node - w238640596-220</t>
-  </si>
-  <si>
     <t>w251239544-400</t>
   </si>
   <si>
     <t>at grid node - w251239544-400</t>
   </si>
   <si>
+    <t>w255293400-400</t>
+  </si>
+  <si>
+    <t>at grid node - w255293400-400</t>
+  </si>
+  <si>
     <t>w255293403-400</t>
   </si>
   <si>
@@ -859,10 +877,40 @@
     <t>at grid node - w255972326-400</t>
   </si>
   <si>
-    <t>w29098336-220</t>
-  </si>
-  <si>
-    <t>at grid node - w29098336-220</t>
+    <t>w276291999-400</t>
+  </si>
+  <si>
+    <t>at grid node - w276291999-400</t>
+  </si>
+  <si>
+    <t>w293484891-400</t>
+  </si>
+  <si>
+    <t>at grid node - w293484891-400</t>
+  </si>
+  <si>
+    <t>w303870256-400</t>
+  </si>
+  <si>
+    <t>at grid node - w303870256-400</t>
+  </si>
+  <si>
+    <t>w32036484-400</t>
+  </si>
+  <si>
+    <t>at grid node - w32036484-400</t>
+  </si>
+  <si>
+    <t>w385118244-400</t>
+  </si>
+  <si>
+    <t>at grid node - w385118244-400</t>
+  </si>
+  <si>
+    <t>w46092396-400</t>
+  </si>
+  <si>
+    <t>at grid node - w46092396-400</t>
   </si>
   <si>
     <t>w46235456-220</t>
@@ -1437,10 +1485,10 @@
         <v>78</v>
       </c>
       <c r="R13" t="s">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="S13" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="T13" t="s">
         <v>226</v>
@@ -1537,10 +1585,10 @@
         <v>78</v>
       </c>
       <c r="R15" t="s">
-        <v>231</v>
+        <v>152</v>
       </c>
       <c r="S15" t="s">
-        <v>232</v>
+        <v>153</v>
       </c>
       <c r="T15" t="s">
         <v>226</v>
@@ -1587,10 +1635,10 @@
         <v>78</v>
       </c>
       <c r="R16" t="s">
-        <v>138</v>
+        <v>231</v>
       </c>
       <c r="S16" t="s">
-        <v>139</v>
+        <v>232</v>
       </c>
       <c r="T16" t="s">
         <v>226</v>
@@ -1737,10 +1785,10 @@
         <v>78</v>
       </c>
       <c r="R19" t="s">
-        <v>237</v>
+        <v>138</v>
       </c>
       <c r="S19" t="s">
-        <v>238</v>
+        <v>139</v>
       </c>
       <c r="T19" t="s">
         <v>226</v>
@@ -1787,10 +1835,10 @@
         <v>78</v>
       </c>
       <c r="R20" t="s">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="S20" t="s">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="T20" t="s">
         <v>226</v>
@@ -1863,10 +1911,10 @@
         <v>78</v>
       </c>
       <c r="R22" t="s">
-        <v>110</v>
+        <v>241</v>
       </c>
       <c r="S22" t="s">
-        <v>111</v>
+        <v>242</v>
       </c>
       <c r="T22" t="s">
         <v>226</v>
@@ -1901,10 +1949,10 @@
         <v>78</v>
       </c>
       <c r="R23" t="s">
-        <v>88</v>
+        <v>243</v>
       </c>
       <c r="S23" t="s">
-        <v>89</v>
+        <v>244</v>
       </c>
       <c r="T23" t="s">
         <v>226</v>
@@ -1939,10 +1987,10 @@
         <v>78</v>
       </c>
       <c r="R24" t="s">
-        <v>112</v>
+        <v>245</v>
       </c>
       <c r="S24" t="s">
-        <v>113</v>
+        <v>246</v>
       </c>
       <c r="T24" t="s">
         <v>226</v>
@@ -1977,10 +2025,10 @@
         <v>78</v>
       </c>
       <c r="R25" t="s">
-        <v>241</v>
+        <v>174</v>
       </c>
       <c r="S25" t="s">
-        <v>242</v>
+        <v>175</v>
       </c>
       <c r="T25" t="s">
         <v>226</v>
@@ -2015,10 +2063,10 @@
         <v>78</v>
       </c>
       <c r="R26" t="s">
-        <v>243</v>
+        <v>110</v>
       </c>
       <c r="S26" t="s">
-        <v>244</v>
+        <v>111</v>
       </c>
       <c r="T26" t="s">
         <v>226</v>
@@ -2053,10 +2101,10 @@
         <v>78</v>
       </c>
       <c r="R27" t="s">
-        <v>245</v>
+        <v>88</v>
       </c>
       <c r="S27" t="s">
-        <v>246</v>
+        <v>89</v>
       </c>
       <c r="T27" t="s">
         <v>226</v>
@@ -2091,10 +2139,10 @@
         <v>78</v>
       </c>
       <c r="R28" t="s">
-        <v>144</v>
+        <v>112</v>
       </c>
       <c r="S28" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="T28" t="s">
         <v>226</v>
@@ -2167,10 +2215,10 @@
         <v>78</v>
       </c>
       <c r="R30" t="s">
-        <v>249</v>
+        <v>144</v>
       </c>
       <c r="S30" t="s">
-        <v>250</v>
+        <v>145</v>
       </c>
       <c r="T30" t="s">
         <v>226</v>
@@ -2205,10 +2253,10 @@
         <v>78</v>
       </c>
       <c r="R31" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="S31" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="T31" t="s">
         <v>226</v>
@@ -2243,10 +2291,10 @@
         <v>78</v>
       </c>
       <c r="R32" t="s">
-        <v>207</v>
+        <v>251</v>
       </c>
       <c r="S32" t="s">
-        <v>208</v>
+        <v>252</v>
       </c>
       <c r="T32" t="s">
         <v>226</v>
@@ -2281,10 +2329,10 @@
         <v>78</v>
       </c>
       <c r="R33" t="s">
-        <v>148</v>
+        <v>253</v>
       </c>
       <c r="S33" t="s">
-        <v>149</v>
+        <v>254</v>
       </c>
       <c r="T33" t="s">
         <v>226</v>
@@ -2319,10 +2367,10 @@
         <v>78</v>
       </c>
       <c r="R34" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="S34" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="T34" t="s">
         <v>226</v>
@@ -2357,10 +2405,10 @@
         <v>78</v>
       </c>
       <c r="R35" t="s">
-        <v>222</v>
+        <v>257</v>
       </c>
       <c r="S35" t="s">
-        <v>223</v>
+        <v>258</v>
       </c>
       <c r="T35" t="s">
         <v>226</v>
@@ -2395,10 +2443,10 @@
         <v>78</v>
       </c>
       <c r="R36" t="s">
-        <v>255</v>
+        <v>207</v>
       </c>
       <c r="S36" t="s">
-        <v>256</v>
+        <v>208</v>
       </c>
       <c r="T36" t="s">
         <v>226</v>
@@ -2433,10 +2481,10 @@
         <v>78</v>
       </c>
       <c r="R37" t="s">
-        <v>257</v>
+        <v>148</v>
       </c>
       <c r="S37" t="s">
-        <v>258</v>
+        <v>149</v>
       </c>
       <c r="T37" t="s">
         <v>226</v>
@@ -2471,10 +2519,10 @@
         <v>78</v>
       </c>
       <c r="R38" t="s">
-        <v>259</v>
+        <v>92</v>
       </c>
       <c r="S38" t="s">
-        <v>260</v>
+        <v>93</v>
       </c>
       <c r="T38" t="s">
         <v>226</v>
@@ -2509,10 +2557,10 @@
         <v>78</v>
       </c>
       <c r="R39" t="s">
-        <v>201</v>
+        <v>259</v>
       </c>
       <c r="S39" t="s">
-        <v>202</v>
+        <v>260</v>
       </c>
       <c r="T39" t="s">
         <v>226</v>
@@ -2585,10 +2633,10 @@
         <v>78</v>
       </c>
       <c r="R41" t="s">
-        <v>172</v>
+        <v>263</v>
       </c>
       <c r="S41" t="s">
-        <v>173</v>
+        <v>264</v>
       </c>
       <c r="T41" t="s">
         <v>226</v>
@@ -2623,10 +2671,10 @@
         <v>78</v>
       </c>
       <c r="R42" t="s">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="S42" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="T42" t="s">
         <v>226</v>
@@ -2699,10 +2747,10 @@
         <v>78</v>
       </c>
       <c r="R44" t="s">
-        <v>162</v>
+        <v>265</v>
       </c>
       <c r="S44" t="s">
-        <v>163</v>
+        <v>266</v>
       </c>
       <c r="T44" t="s">
         <v>226</v>
@@ -2737,10 +2785,10 @@
         <v>78</v>
       </c>
       <c r="R45" t="s">
-        <v>263</v>
+        <v>180</v>
       </c>
       <c r="S45" t="s">
-        <v>264</v>
+        <v>181</v>
       </c>
       <c r="T45" t="s">
         <v>226</v>
@@ -2775,10 +2823,10 @@
         <v>78</v>
       </c>
       <c r="R46" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="S46" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="T46" t="s">
         <v>226</v>
@@ -2813,10 +2861,10 @@
         <v>78</v>
       </c>
       <c r="R47" t="s">
-        <v>267</v>
+        <v>162</v>
       </c>
       <c r="S47" t="s">
-        <v>268</v>
+        <v>163</v>
       </c>
       <c r="T47" t="s">
         <v>226</v>
@@ -2851,10 +2899,10 @@
         <v>78</v>
       </c>
       <c r="R48" t="s">
-        <v>84</v>
+        <v>269</v>
       </c>
       <c r="S48" t="s">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c r="T48" t="s">
         <v>226</v>
@@ -2889,10 +2937,10 @@
         <v>78</v>
       </c>
       <c r="R49" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="S49" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="T49" t="s">
         <v>226</v>
@@ -2927,10 +2975,10 @@
         <v>78</v>
       </c>
       <c r="R50" t="s">
-        <v>271</v>
+        <v>84</v>
       </c>
       <c r="S50" t="s">
-        <v>272</v>
+        <v>85</v>
       </c>
       <c r="T50" t="s">
         <v>226</v>
@@ -2965,10 +3013,10 @@
         <v>78</v>
       </c>
       <c r="R51" t="s">
-        <v>273</v>
+        <v>176</v>
       </c>
       <c r="S51" t="s">
-        <v>274</v>
+        <v>177</v>
       </c>
       <c r="T51" t="s">
         <v>226</v>
@@ -3003,10 +3051,10 @@
         <v>78</v>
       </c>
       <c r="R52" t="s">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="S52" t="s">
-        <v>83</v>
+        <v>274</v>
       </c>
       <c r="T52" t="s">
         <v>226</v>
@@ -3041,10 +3089,10 @@
         <v>78</v>
       </c>
       <c r="R53" t="s">
-        <v>164</v>
+        <v>275</v>
       </c>
       <c r="S53" t="s">
-        <v>165</v>
+        <v>276</v>
       </c>
       <c r="T53" t="s">
         <v>226</v>
@@ -3079,10 +3127,10 @@
         <v>78</v>
       </c>
       <c r="R54" t="s">
-        <v>220</v>
+        <v>277</v>
       </c>
       <c r="S54" t="s">
-        <v>221</v>
+        <v>278</v>
       </c>
       <c r="T54" t="s">
         <v>226</v>
@@ -3117,10 +3165,10 @@
         <v>78</v>
       </c>
       <c r="R55" t="s">
-        <v>114</v>
+        <v>140</v>
       </c>
       <c r="S55" t="s">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="T55" t="s">
         <v>226</v>
@@ -3155,10 +3203,10 @@
         <v>78</v>
       </c>
       <c r="R56" t="s">
-        <v>182</v>
+        <v>279</v>
       </c>
       <c r="S56" t="s">
-        <v>183</v>
+        <v>280</v>
       </c>
       <c r="T56" t="s">
         <v>226</v>
@@ -3193,10 +3241,10 @@
         <v>78</v>
       </c>
       <c r="R57" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="S57" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="T57" t="s">
         <v>226</v>
@@ -3231,10 +3279,10 @@
         <v>78</v>
       </c>
       <c r="R58" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="S58" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="T58" t="s">
         <v>226</v>
@@ -3269,10 +3317,10 @@
         <v>78</v>
       </c>
       <c r="R59" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="S59" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="T59" t="s">
         <v>226</v>
@@ -3307,10 +3355,10 @@
         <v>78</v>
       </c>
       <c r="R60" t="s">
-        <v>154</v>
+        <v>283</v>
       </c>
       <c r="S60" t="s">
-        <v>155</v>
+        <v>284</v>
       </c>
       <c r="T60" t="s">
         <v>226</v>
@@ -3345,10 +3393,10 @@
         <v>78</v>
       </c>
       <c r="R61" t="s">
-        <v>170</v>
+        <v>285</v>
       </c>
       <c r="S61" t="s">
-        <v>171</v>
+        <v>286</v>
       </c>
       <c r="T61" t="s">
         <v>226</v>
@@ -3383,10 +3431,10 @@
         <v>78</v>
       </c>
       <c r="R62" t="s">
-        <v>126</v>
+        <v>220</v>
       </c>
       <c r="S62" t="s">
-        <v>127</v>
+        <v>221</v>
       </c>
       <c r="T62" t="s">
         <v>226</v>
@@ -3421,10 +3469,10 @@
         <v>78</v>
       </c>
       <c r="R63" t="s">
-        <v>98</v>
+        <v>287</v>
       </c>
       <c r="S63" t="s">
-        <v>99</v>
+        <v>288</v>
       </c>
       <c r="T63" t="s">
         <v>226</v>
@@ -3459,10 +3507,10 @@
         <v>78</v>
       </c>
       <c r="R64" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="S64" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="T64" t="s">
         <v>226</v>
@@ -3497,10 +3545,10 @@
         <v>78</v>
       </c>
       <c r="R65" t="s">
-        <v>277</v>
+        <v>182</v>
       </c>
       <c r="S65" t="s">
-        <v>278</v>
+        <v>183</v>
       </c>
       <c r="T65" t="s">
         <v>226</v>
@@ -3535,10 +3583,10 @@
         <v>78</v>
       </c>
       <c r="R66" t="s">
-        <v>160</v>
+        <v>289</v>
       </c>
       <c r="S66" t="s">
-        <v>161</v>
+        <v>290</v>
       </c>
       <c r="T66" t="s">
         <v>226</v>
@@ -3573,10 +3621,10 @@
         <v>78</v>
       </c>
       <c r="R67" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="S67" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="T67" t="s">
         <v>226</v>
@@ -3607,6 +3655,18 @@
       <c r="O68" t="s">
         <v>215</v>
       </c>
+      <c r="Q68" t="s">
+        <v>78</v>
+      </c>
+      <c r="R68" t="s">
+        <v>130</v>
+      </c>
+      <c r="S68" t="s">
+        <v>131</v>
+      </c>
+      <c r="T68" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
@@ -3633,6 +3693,18 @@
       <c r="O69" t="s">
         <v>215</v>
       </c>
+      <c r="Q69" t="s">
+        <v>78</v>
+      </c>
+      <c r="R69" t="s">
+        <v>154</v>
+      </c>
+      <c r="S69" t="s">
+        <v>155</v>
+      </c>
+      <c r="T69" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.45">
       <c r="L70" t="s">
@@ -3647,6 +3719,18 @@
       <c r="O70" t="s">
         <v>215</v>
       </c>
+      <c r="Q70" t="s">
+        <v>78</v>
+      </c>
+      <c r="R70" t="s">
+        <v>170</v>
+      </c>
+      <c r="S70" t="s">
+        <v>171</v>
+      </c>
+      <c r="T70" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.45">
       <c r="L71" t="s">
@@ -3661,6 +3745,18 @@
       <c r="O71" t="s">
         <v>215</v>
       </c>
+      <c r="Q71" t="s">
+        <v>78</v>
+      </c>
+      <c r="R71" t="s">
+        <v>146</v>
+      </c>
+      <c r="S71" t="s">
+        <v>147</v>
+      </c>
+      <c r="T71" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.45">
       <c r="L72" t="s">
@@ -3675,6 +3771,18 @@
       <c r="O72" t="s">
         <v>215</v>
       </c>
+      <c r="Q72" t="s">
+        <v>78</v>
+      </c>
+      <c r="R72" t="s">
+        <v>142</v>
+      </c>
+      <c r="S72" t="s">
+        <v>143</v>
+      </c>
+      <c r="T72" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.45">
       <c r="L73" t="s">
@@ -3689,6 +3797,18 @@
       <c r="O73" t="s">
         <v>215</v>
       </c>
+      <c r="Q73" t="s">
+        <v>78</v>
+      </c>
+      <c r="R73" t="s">
+        <v>293</v>
+      </c>
+      <c r="S73" t="s">
+        <v>294</v>
+      </c>
+      <c r="T73" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="74" spans="2:20" x14ac:dyDescent="0.45">
       <c r="L74" t="s">
@@ -3703,6 +3823,18 @@
       <c r="O74" t="s">
         <v>215</v>
       </c>
+      <c r="Q74" t="s">
+        <v>78</v>
+      </c>
+      <c r="R74" t="s">
+        <v>160</v>
+      </c>
+      <c r="S74" t="s">
+        <v>161</v>
+      </c>
+      <c r="T74" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.45">
       <c r="L75" t="s">
@@ -3716,6 +3848,18 @@
       </c>
       <c r="O75" t="s">
         <v>215</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>78</v>
+      </c>
+      <c r="R75" t="s">
+        <v>295</v>
+      </c>
+      <c r="S75" t="s">
+        <v>296</v>
+      </c>
+      <c r="T75" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.45">

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A22CBADA-3AED-4B05-86C3-03C8FC8E8FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B7DAD73-A8CC-4707-810B-55C5E308A5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B7DAD73-A8CC-4707-810B-55C5E308A5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{42C48B90-6C1F-4069-ABB3-2A7AC2F334C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="257">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -307,37 +307,349 @@
     <t>POL</t>
   </si>
   <si>
+    <t>w66161634-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w66161634-220_POL</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS,Bioenergy - Large scale unit,CCGT,CCGT + CCS,Coal + CCS,Gas turbine,IGCC,IGCC + CCS,Nuclear large,Oxyfuel + CCS,Steam Coal - SUBCRITICAL,Steam Coal - SUPERCRITICAL,Steam Coal - ULTRASUPERCRITICAL</t>
+  </si>
+  <si>
+    <t>w681264796-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w681264796-400_POL</t>
+  </si>
+  <si>
+    <t>w293489663-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w293489663-400_POL</t>
+  </si>
+  <si>
+    <t>w98634956-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w98634956-220_POL</t>
+  </si>
+  <si>
+    <t>PL14-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - PL14-220_POL</t>
+  </si>
+  <si>
+    <t>w29139402-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w29139402-220_POL</t>
+  </si>
+  <si>
+    <t>w224727316-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w224727316-220_POL</t>
+  </si>
+  <si>
+    <t>PL11-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - PL11-400_POL</t>
+  </si>
+  <si>
+    <t>w112614319-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w112614319-400_POL</t>
+  </si>
+  <si>
+    <t>w130644710-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w130644710-400_POL</t>
+  </si>
+  <si>
+    <t>w293489607-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w293489607-400_POL</t>
+  </si>
+  <si>
+    <t>w385539724-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w385539724-220_POL</t>
+  </si>
+  <si>
+    <t>PL54-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - PL54-220_POL</t>
+  </si>
+  <si>
+    <t>w216975352-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w216975352-220_POL</t>
+  </si>
+  <si>
+    <t>w173582810-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w173582810-220_POL</t>
+  </si>
+  <si>
+    <t>w115801644-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w115801644-220_POL</t>
+  </si>
+  <si>
+    <t>w66161634-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w66161634-400_POL</t>
+  </si>
+  <si>
+    <t>w183945016-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w183945016-220_POL</t>
+  </si>
+  <si>
+    <t>w101982559-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w101982559-220_POL</t>
+  </si>
+  <si>
+    <t>w35366436-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w35366436-220_POL</t>
+  </si>
+  <si>
+    <t>w255277953-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w255277953-400_POL</t>
+  </si>
+  <si>
+    <t>w121656686-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w121656686-220_POL</t>
+  </si>
+  <si>
+    <t>w255284259-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w255284259-220_POL</t>
+  </si>
+  <si>
+    <t>w199098053-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w199098053-400_POL</t>
+  </si>
+  <si>
+    <t>w40062974-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w40062974-220_POL</t>
+  </si>
+  <si>
+    <t>w293484894-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w293484894-220_POL</t>
+  </si>
+  <si>
+    <t>w88544449-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w88544449-220_POL</t>
+  </si>
+  <si>
+    <t>PL59-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - PL59-220_POL</t>
+  </si>
+  <si>
+    <t>PL38-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - PL38-400_POL</t>
+  </si>
+  <si>
+    <t>w89434732-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w89434732-220_POL</t>
+  </si>
+  <si>
+    <t>r9399771-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - r9399771-220_POL</t>
+  </si>
+  <si>
+    <t>w189501431-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w189501431-400_POL</t>
+  </si>
+  <si>
+    <t>PL7-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - PL7-400_POL</t>
+  </si>
+  <si>
+    <t>PL40-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - PL40-220_POL</t>
+  </si>
+  <si>
+    <t>w255232597-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w255232597-220_POL</t>
+  </si>
+  <si>
+    <t>w79033485-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w79033485-400_POL</t>
+  </si>
+  <si>
+    <t>w25898810-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w25898810-220_POL</t>
+  </si>
+  <si>
+    <t>w40946790-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w40946790-220_POL</t>
+  </si>
+  <si>
+    <t>w180535363-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w180535363-220_POL</t>
+  </si>
+  <si>
+    <t>w198635989-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w198635989-220_POL</t>
+  </si>
+  <si>
+    <t>w255972397-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w255972397-400_POL</t>
+  </si>
+  <si>
+    <t>w143484238-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w143484238-220_POL</t>
+  </si>
+  <si>
+    <t>PL30-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - PL30-220_POL</t>
+  </si>
+  <si>
+    <t>w726776987-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w726776987-220_POL</t>
+  </si>
+  <si>
+    <t>w72879943-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w72879943-220_POL</t>
+  </si>
+  <si>
+    <t>w170249563-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w170249563-220_POL</t>
+  </si>
+  <si>
+    <t>w46092396-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w46092396-220_POL</t>
+  </si>
+  <si>
+    <t>w658600169-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w658600169-400_POL</t>
+  </si>
+  <si>
+    <t>w135598292-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w135598292-220_POL</t>
+  </si>
+  <si>
+    <t>PL18-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - PL18-400_POL</t>
+  </si>
+  <si>
+    <t>w171383831-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w171383831-220_POL</t>
+  </si>
+  <si>
+    <t>PL1-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - PL1-400_POL</t>
+  </si>
+  <si>
+    <t>w171917072-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w171917072-400_POL</t>
+  </si>
+  <si>
+    <t>w185454704-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w185454704-220_POL</t>
+  </si>
+  <si>
+    <t>w254938713-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w254938713-400_POL</t>
+  </si>
+  <si>
     <t>w40946784-400_POL</t>
   </si>
   <si>
     <t>at grid node - w40946784-400_POL</t>
   </si>
   <si>
-    <t>Bioenergy + CCUS,Bioenergy - Large scale unit,CCGT,CCGT + CCS,Coal + CCS,Gas turbine,IGCC,IGCC + CCS,Nuclear large,Oxyfuel + CCS,Steam Coal - SUBCRITICAL,Steam Coal - SUPERCRITICAL,Steam Coal - ULTRASUPERCRITICAL</t>
-  </si>
-  <si>
-    <t>w29139402-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w29139402-220_POL</t>
-  </si>
-  <si>
-    <t>w254938713-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w254938713-400_POL</t>
-  </si>
-  <si>
-    <t>PL1-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL1-400_POL</t>
-  </si>
-  <si>
-    <t>w115801644-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w115801644-220_POL</t>
+    <t>w191352746-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w191352746-220_POL</t>
   </si>
   <si>
     <t>PL16-400_POL</t>
@@ -346,324 +658,18 @@
     <t>at grid node - PL16-400_POL</t>
   </si>
   <si>
-    <t>w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>w135598292-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w135598292-220_POL</t>
-  </si>
-  <si>
-    <t>w191352746-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w191352746-220_POL</t>
-  </si>
-  <si>
-    <t>w72879943-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w72879943-220_POL</t>
-  </si>
-  <si>
-    <t>w171383831-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w171383831-220_POL</t>
-  </si>
-  <si>
-    <t>w185454704-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w185454704-220_POL</t>
-  </si>
-  <si>
-    <t>PL14-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL14-220_POL</t>
-  </si>
-  <si>
-    <t>w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>PL11-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL11-400_POL</t>
-  </si>
-  <si>
-    <t>w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>w130644710-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w130644710-400_POL</t>
-  </si>
-  <si>
-    <t>w385539724-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w385539724-220_POL</t>
-  </si>
-  <si>
-    <t>w46092396-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w46092396-220_POL</t>
-  </si>
-  <si>
-    <t>w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>PL18-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL18-400_POL</t>
-  </si>
-  <si>
-    <t>w173582810-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w173582810-220_POL</t>
-  </si>
-  <si>
-    <t>w35366436-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w35366436-220_POL</t>
-  </si>
-  <si>
-    <t>w726776987-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w726776987-220_POL</t>
-  </si>
-  <si>
-    <t>w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>w293484894-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w293484894-220_POL</t>
-  </si>
-  <si>
-    <t>PL59-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL59-220_POL</t>
-  </si>
-  <si>
-    <t>w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>PL38-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL38-400_POL</t>
-  </si>
-  <si>
-    <t>w255972397-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w255972397-400_POL</t>
-  </si>
-  <si>
-    <t>w89434732-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w89434732-220_POL</t>
-  </si>
-  <si>
-    <t>w143484238-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w143484238-220_POL</t>
-  </si>
-  <si>
-    <t>w79033485-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w79033485-400_POL</t>
-  </si>
-  <si>
-    <t>w170249563-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w170249563-220_POL</t>
-  </si>
-  <si>
-    <t>w25898810-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w25898810-220_POL</t>
-  </si>
-  <si>
-    <t>PL30-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL30-220_POL</t>
-  </si>
-  <si>
-    <t>w66161634-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w66161634-220_POL</t>
-  </si>
-  <si>
-    <t>w681264796-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w681264796-400_POL</t>
-  </si>
-  <si>
-    <t>w293489663-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w293489663-400_POL</t>
-  </si>
-  <si>
-    <t>w98634956-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w98634956-220_POL</t>
-  </si>
-  <si>
-    <t>w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>w293489607-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w293489607-400_POL</t>
-  </si>
-  <si>
-    <t>PL54-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL54-400_POL</t>
-  </si>
-  <si>
-    <t>w216975352-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w216975352-220_POL</t>
-  </si>
-  <si>
-    <t>w66161634-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w66161634-400_POL</t>
-  </si>
-  <si>
-    <t>w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>w101982559-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w101982559-220_POL</t>
-  </si>
-  <si>
-    <t>w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>w255284259-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w255284259-220_POL</t>
-  </si>
-  <si>
-    <t>w199098053-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w199098053-400_POL</t>
-  </si>
-  <si>
-    <t>w40062974-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w40062974-220_POL</t>
-  </si>
-  <si>
-    <t>w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>r9399771-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - r9399771-220_POL</t>
-  </si>
-  <si>
-    <t>w189501431-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w189501431-400_POL</t>
-  </si>
-  <si>
-    <t>PL7-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL7-400_POL</t>
-  </si>
-  <si>
-    <t>PL40-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL40-220_POL</t>
-  </si>
-  <si>
-    <t>w255232597-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w255232597-220_POL</t>
-  </si>
-  <si>
     <t>w184899160-220_POL</t>
   </si>
   <si>
     <t>at grid node - w184899160-220_POL</t>
   </si>
   <si>
+    <t>w255284259-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w255284259-400_POL</t>
+  </si>
+  <si>
     <t>w158232924-220_POL</t>
   </si>
   <si>
@@ -691,28 +697,28 @@
     <t>at grid node - w98611253-220_POL</t>
   </si>
   <si>
+    <t>PL19-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - PL19-220_POL</t>
+  </si>
+  <si>
+    <t>w166838338-400_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w166838338-400_POL</t>
+  </si>
+  <si>
+    <t>w178838661-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w178838661-220_POL</t>
+  </si>
+  <si>
     <t>w166710856-400_POL</t>
   </si>
   <si>
     <t>at grid node - w166710856-400_POL</t>
-  </si>
-  <si>
-    <t>PL19-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL19-220_POL</t>
-  </si>
-  <si>
-    <t>w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>w178838661-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w178838661-220_POL</t>
   </si>
   <si>
     <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
@@ -1130,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:T81"/>
+  <dimension ref="B3:T82"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="3" spans="2:20" x14ac:dyDescent="0.45">
@@ -1235,13 +1241,13 @@
         <v>88</v>
       </c>
       <c r="H11" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="J11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L11" t="s">
         <v>88</v>
@@ -1253,19 +1259,19 @@
         <v>90</v>
       </c>
       <c r="O11" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q11" t="s">
         <v>88</v>
       </c>
       <c r="R11" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="S11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="T11" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
@@ -1285,13 +1291,13 @@
         <v>88</v>
       </c>
       <c r="H12" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I12" t="s">
+        <v>214</v>
+      </c>
+      <c r="J12" t="s">
         <v>212</v>
-      </c>
-      <c r="J12" t="s">
-        <v>210</v>
       </c>
       <c r="L12" t="s">
         <v>88</v>
@@ -1303,19 +1309,19 @@
         <v>93</v>
       </c>
       <c r="O12" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q12" t="s">
         <v>88</v>
       </c>
       <c r="R12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="S12" t="s">
+        <v>240</v>
+      </c>
+      <c r="T12" t="s">
         <v>238</v>
-      </c>
-      <c r="T12" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
@@ -1335,13 +1341,13 @@
         <v>88</v>
       </c>
       <c r="H13" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I13" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J13" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L13" t="s">
         <v>88</v>
@@ -1353,19 +1359,19 @@
         <v>95</v>
       </c>
       <c r="O13" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q13" t="s">
         <v>88</v>
       </c>
       <c r="R13" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="S13" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="T13" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
@@ -1385,13 +1391,13 @@
         <v>88</v>
       </c>
       <c r="H14" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="I14" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="J14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L14" t="s">
         <v>88</v>
@@ -1403,19 +1409,19 @@
         <v>97</v>
       </c>
       <c r="O14" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q14" t="s">
         <v>88</v>
       </c>
       <c r="R14" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="S14" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="T14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
@@ -1435,13 +1441,13 @@
         <v>88</v>
       </c>
       <c r="H15" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I15" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="J15" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L15" t="s">
         <v>88</v>
@@ -1453,19 +1459,19 @@
         <v>99</v>
       </c>
       <c r="O15" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q15" t="s">
         <v>88</v>
       </c>
       <c r="R15" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="S15" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="T15" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
@@ -1485,13 +1491,13 @@
         <v>88</v>
       </c>
       <c r="H16" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I16" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J16" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L16" t="s">
         <v>88</v>
@@ -1503,19 +1509,19 @@
         <v>101</v>
       </c>
       <c r="O16" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q16" t="s">
         <v>88</v>
       </c>
       <c r="R16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="S16" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="T16" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
@@ -1535,13 +1541,13 @@
         <v>88</v>
       </c>
       <c r="H17" t="s">
-        <v>221</v>
+        <v>178</v>
       </c>
       <c r="I17" t="s">
-        <v>222</v>
+        <v>179</v>
       </c>
       <c r="J17" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L17" t="s">
         <v>88</v>
@@ -1553,19 +1559,19 @@
         <v>103</v>
       </c>
       <c r="O17" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q17" t="s">
         <v>88</v>
       </c>
       <c r="R17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="S17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="T17" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
@@ -1585,13 +1591,13 @@
         <v>88</v>
       </c>
       <c r="H18" t="s">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="I18" t="s">
-        <v>109</v>
+        <v>193</v>
       </c>
       <c r="J18" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L18" t="s">
         <v>88</v>
@@ -1603,19 +1609,19 @@
         <v>105</v>
       </c>
       <c r="O18" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q18" t="s">
         <v>88</v>
       </c>
       <c r="R18" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="S18" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="T18" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
@@ -1635,13 +1641,13 @@
         <v>88</v>
       </c>
       <c r="H19" t="s">
-        <v>96</v>
+        <v>223</v>
       </c>
       <c r="I19" t="s">
-        <v>97</v>
+        <v>224</v>
       </c>
       <c r="J19" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L19" t="s">
         <v>88</v>
@@ -1653,19 +1659,19 @@
         <v>107</v>
       </c>
       <c r="O19" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q19" t="s">
         <v>88</v>
       </c>
       <c r="R19" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="S19" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="T19" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
@@ -1685,13 +1691,13 @@
         <v>88</v>
       </c>
       <c r="H20" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I20" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="J20" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="L20" t="s">
         <v>88</v>
@@ -1703,19 +1709,19 @@
         <v>109</v>
       </c>
       <c r="O20" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q20" t="s">
         <v>88</v>
       </c>
       <c r="R20" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="S20" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="T20" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
@@ -1735,25 +1741,25 @@
         <v>88</v>
       </c>
       <c r="M21" t="s">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="N21" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="O21" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q21" t="s">
         <v>88</v>
       </c>
       <c r="R21" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="S21" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="T21" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.45">
@@ -1773,25 +1779,25 @@
         <v>88</v>
       </c>
       <c r="M22" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="N22" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="O22" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q22" t="s">
         <v>88</v>
       </c>
       <c r="R22" t="s">
-        <v>168</v>
+        <v>94</v>
       </c>
       <c r="S22" t="s">
-        <v>169</v>
+        <v>95</v>
       </c>
       <c r="T22" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
@@ -1811,25 +1817,25 @@
         <v>88</v>
       </c>
       <c r="M23" t="s">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="N23" t="s">
-        <v>191</v>
+        <v>115</v>
       </c>
       <c r="O23" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q23" t="s">
         <v>88</v>
       </c>
       <c r="R23" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S23" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="T23" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
@@ -1849,25 +1855,25 @@
         <v>88</v>
       </c>
       <c r="M24" t="s">
-        <v>200</v>
+        <v>116</v>
       </c>
       <c r="N24" t="s">
-        <v>201</v>
+        <v>117</v>
       </c>
       <c r="O24" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q24" t="s">
         <v>88</v>
       </c>
       <c r="R24" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="S24" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="T24" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">
@@ -1887,25 +1893,25 @@
         <v>88</v>
       </c>
       <c r="M25" t="s">
-        <v>192</v>
+        <v>118</v>
       </c>
       <c r="N25" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="O25" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q25" t="s">
         <v>88</v>
       </c>
       <c r="R25" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="S25" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="T25" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.45">
@@ -1925,13 +1931,13 @@
         <v>88</v>
       </c>
       <c r="M26" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="N26" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="O26" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q26" t="s">
         <v>88</v>
@@ -1943,7 +1949,7 @@
         <v>224</v>
       </c>
       <c r="T26" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.45">
@@ -1963,13 +1969,13 @@
         <v>88</v>
       </c>
       <c r="M27" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="N27" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="O27" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.45">
@@ -1989,13 +1995,13 @@
         <v>88</v>
       </c>
       <c r="M28" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="N28" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="O28" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.45">
@@ -2015,13 +2021,13 @@
         <v>88</v>
       </c>
       <c r="M29" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="N29" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="O29" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.45">
@@ -2041,13 +2047,13 @@
         <v>88</v>
       </c>
       <c r="M30" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="N30" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="O30" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.45">
@@ -2067,13 +2073,13 @@
         <v>88</v>
       </c>
       <c r="M31" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="N31" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="O31" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.45">
@@ -2093,13 +2099,13 @@
         <v>88</v>
       </c>
       <c r="M32" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="N32" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="O32" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.45">
@@ -2119,13 +2125,13 @@
         <v>88</v>
       </c>
       <c r="M33" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="N33" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="O33" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.45">
@@ -2145,13 +2151,13 @@
         <v>88</v>
       </c>
       <c r="M34" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="N34" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="O34" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="2:15" x14ac:dyDescent="0.45">
@@ -2171,13 +2177,13 @@
         <v>88</v>
       </c>
       <c r="M35" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="N35" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="O35" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="36" spans="2:15" x14ac:dyDescent="0.45">
@@ -2197,13 +2203,13 @@
         <v>88</v>
       </c>
       <c r="M36" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="N36" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="O36" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="2:15" x14ac:dyDescent="0.45">
@@ -2223,13 +2229,13 @@
         <v>88</v>
       </c>
       <c r="M37" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="N37" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="O37" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="2:15" x14ac:dyDescent="0.45">
@@ -2249,13 +2255,13 @@
         <v>88</v>
       </c>
       <c r="M38" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="N38" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="O38" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="2:15" x14ac:dyDescent="0.45">
@@ -2275,13 +2281,13 @@
         <v>88</v>
       </c>
       <c r="M39" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="N39" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="O39" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="2:15" x14ac:dyDescent="0.45">
@@ -2301,13 +2307,13 @@
         <v>88</v>
       </c>
       <c r="M40" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="N40" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="O40" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="41" spans="2:15" x14ac:dyDescent="0.45">
@@ -2327,13 +2333,13 @@
         <v>88</v>
       </c>
       <c r="M41" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="N41" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="O41" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="42" spans="2:15" x14ac:dyDescent="0.45">
@@ -2353,13 +2359,13 @@
         <v>88</v>
       </c>
       <c r="M42" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="N42" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="O42" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="43" spans="2:15" x14ac:dyDescent="0.45">
@@ -2379,13 +2385,13 @@
         <v>88</v>
       </c>
       <c r="M43" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="N43" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="O43" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="44" spans="2:15" x14ac:dyDescent="0.45">
@@ -2405,13 +2411,13 @@
         <v>88</v>
       </c>
       <c r="M44" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="N44" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="O44" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="45" spans="2:15" x14ac:dyDescent="0.45">
@@ -2431,13 +2437,13 @@
         <v>88</v>
       </c>
       <c r="M45" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="N45" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="O45" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="46" spans="2:15" x14ac:dyDescent="0.45">
@@ -2457,13 +2463,13 @@
         <v>88</v>
       </c>
       <c r="M46" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="N46" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="O46" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="47" spans="2:15" x14ac:dyDescent="0.45">
@@ -2483,13 +2489,13 @@
         <v>88</v>
       </c>
       <c r="M47" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N47" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="O47" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="48" spans="2:15" x14ac:dyDescent="0.45">
@@ -2509,13 +2515,13 @@
         <v>88</v>
       </c>
       <c r="M48" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="N48" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="O48" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49" spans="2:15" x14ac:dyDescent="0.45">
@@ -2535,13 +2541,13 @@
         <v>88</v>
       </c>
       <c r="M49" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="N49" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="O49" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="2:15" x14ac:dyDescent="0.45">
@@ -2561,13 +2567,13 @@
         <v>88</v>
       </c>
       <c r="M50" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="N50" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="O50" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.45">
@@ -2587,13 +2593,13 @@
         <v>88</v>
       </c>
       <c r="M51" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="N51" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="O51" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.45">
@@ -2613,13 +2619,13 @@
         <v>88</v>
       </c>
       <c r="M52" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="N52" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="O52" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.45">
@@ -2639,13 +2645,13 @@
         <v>88</v>
       </c>
       <c r="M53" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="N53" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="O53" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="54" spans="2:15" x14ac:dyDescent="0.45">
@@ -2665,13 +2671,13 @@
         <v>88</v>
       </c>
       <c r="M54" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="N54" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="O54" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="55" spans="2:15" x14ac:dyDescent="0.45">
@@ -2691,13 +2697,13 @@
         <v>88</v>
       </c>
       <c r="M55" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="N55" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="O55" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="56" spans="2:15" x14ac:dyDescent="0.45">
@@ -2717,13 +2723,13 @@
         <v>88</v>
       </c>
       <c r="M56" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="N56" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="O56" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="57" spans="2:15" x14ac:dyDescent="0.45">
@@ -2743,13 +2749,13 @@
         <v>88</v>
       </c>
       <c r="M57" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="N57" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="O57" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="58" spans="2:15" x14ac:dyDescent="0.45">
@@ -2769,13 +2775,13 @@
         <v>88</v>
       </c>
       <c r="M58" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="N58" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="O58" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="59" spans="2:15" x14ac:dyDescent="0.45">
@@ -2795,13 +2801,13 @@
         <v>88</v>
       </c>
       <c r="M59" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="N59" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="O59" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="60" spans="2:15" x14ac:dyDescent="0.45">
@@ -2821,13 +2827,13 @@
         <v>88</v>
       </c>
       <c r="M60" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="N60" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="O60" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="61" spans="2:15" x14ac:dyDescent="0.45">
@@ -2847,13 +2853,13 @@
         <v>88</v>
       </c>
       <c r="M61" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="N61" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="O61" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="2:15" x14ac:dyDescent="0.45">
@@ -2873,13 +2879,13 @@
         <v>88</v>
       </c>
       <c r="M62" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="N62" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="O62" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="63" spans="2:15" x14ac:dyDescent="0.45">
@@ -2899,13 +2905,13 @@
         <v>88</v>
       </c>
       <c r="M63" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="N63" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="O63" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="64" spans="2:15" x14ac:dyDescent="0.45">
@@ -2925,13 +2931,13 @@
         <v>88</v>
       </c>
       <c r="M64" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="N64" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="O64" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="65" spans="2:15" x14ac:dyDescent="0.45">
@@ -2951,13 +2957,13 @@
         <v>88</v>
       </c>
       <c r="M65" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="N65" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="O65" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="66" spans="2:15" x14ac:dyDescent="0.45">
@@ -2977,13 +2983,13 @@
         <v>88</v>
       </c>
       <c r="M66" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
       <c r="N66" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="O66" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="67" spans="2:15" x14ac:dyDescent="0.45">
@@ -3003,13 +3009,13 @@
         <v>88</v>
       </c>
       <c r="M67" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="N67" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="O67" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="68" spans="2:15" x14ac:dyDescent="0.45">
@@ -3029,13 +3035,13 @@
         <v>88</v>
       </c>
       <c r="M68" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="N68" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="O68" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="69" spans="2:15" x14ac:dyDescent="0.45">
@@ -3055,27 +3061,39 @@
         <v>88</v>
       </c>
       <c r="M69" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="N69" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="O69" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B70" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" t="s">
+        <v>208</v>
+      </c>
+      <c r="D70" t="s">
+        <v>209</v>
+      </c>
+      <c r="E70" t="s">
+        <v>91</v>
+      </c>
       <c r="L70" t="s">
         <v>88</v>
       </c>
       <c r="M70" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="N70" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O70" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="71" spans="2:15" x14ac:dyDescent="0.45">
@@ -3089,7 +3107,7 @@
         <v>229</v>
       </c>
       <c r="O71" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="72" spans="2:15" x14ac:dyDescent="0.45">
@@ -3103,7 +3121,7 @@
         <v>231</v>
       </c>
       <c r="O72" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="73" spans="2:15" x14ac:dyDescent="0.45">
@@ -3117,7 +3135,7 @@
         <v>233</v>
       </c>
       <c r="O73" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="74" spans="2:15" x14ac:dyDescent="0.45">
@@ -3125,13 +3143,13 @@
         <v>88</v>
       </c>
       <c r="M74" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="N74" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="O74" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="75" spans="2:15" x14ac:dyDescent="0.45">
@@ -3139,13 +3157,13 @@
         <v>88</v>
       </c>
       <c r="M75" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
       <c r="N75" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="O75" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="76" spans="2:15" x14ac:dyDescent="0.45">
@@ -3153,13 +3171,13 @@
         <v>88</v>
       </c>
       <c r="M76" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="N76" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="O76" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="77" spans="2:15" x14ac:dyDescent="0.45">
@@ -3167,13 +3185,13 @@
         <v>88</v>
       </c>
       <c r="M77" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="N77" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="O77" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="78" spans="2:15" x14ac:dyDescent="0.45">
@@ -3181,13 +3199,13 @@
         <v>88</v>
       </c>
       <c r="M78" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="N78" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="O78" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="79" spans="2:15" x14ac:dyDescent="0.45">
@@ -3195,13 +3213,13 @@
         <v>88</v>
       </c>
       <c r="M79" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="N79" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="O79" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="80" spans="2:15" x14ac:dyDescent="0.45">
@@ -3209,13 +3227,13 @@
         <v>88</v>
       </c>
       <c r="M80" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N80" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="O80" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="81" spans="12:15" x14ac:dyDescent="0.45">
@@ -3223,13 +3241,27 @@
         <v>88</v>
       </c>
       <c r="M81" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="N81" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="O81" t="s">
-        <v>225</v>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="82" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L82" t="s">
+        <v>88</v>
+      </c>
+      <c r="M82" t="s">
+        <v>208</v>
+      </c>
+      <c r="N82" t="s">
+        <v>209</v>
+      </c>
+      <c r="O82" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42C48B90-6C1F-4069-ABB3-2A7AC2F334C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{16F8CD21-D8A0-41AD-8881-A04A9633E945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16F8CD21-D8A0-41AD-8881-A04A9633E945}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D2C9E1F-217F-45F9-A10A-2FC97388DDA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="258">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -668,6 +668,9 @@
   </si>
   <si>
     <t>at grid node - w255284259-400_POL</t>
+  </si>
+  <si>
+    <t>VERVESTACKS - the open USE platform · Powered by data · Shaped by vision · Guided by intuition · Fueled by passion</t>
   </si>
   <si>
     <t>w158232924-220_POL</t>
@@ -815,7 +818,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -830,16 +833,61 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="7"/>
+      <color rgb="FF969696"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF19375F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F9FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -847,15 +895,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -871,6 +956,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>63500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1054100</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>266700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AFB8134-C140-0F24-F697-C8186D73AF0F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5245100" y="12700"/>
+          <a:ext cx="990600" cy="254000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1136,15 +1276,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:T82"/>
+  <dimension ref="A1:T82"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="10.59765625" customWidth="1"/>
+    <col min="3" max="3" width="16.46484375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.59765625" customWidth="1"/>
+    <col min="7" max="7" width="10.59765625" customWidth="1"/>
+    <col min="8" max="8" width="16.46484375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.59765625" customWidth="1"/>
+    <col min="12" max="12" width="10.59765625" customWidth="1"/>
+    <col min="13" max="13" width="16.46484375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.06640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.59765625" customWidth="1"/>
+    <col min="18" max="18" width="16.46484375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="27" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.59765625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -1152,7 +1322,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>59</v>
       </c>
@@ -1160,2112 +1330,2116 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B9" t="s">
+    <row r="9" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="B9" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="Q9" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B10" t="s">
+    <row r="10" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="B10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="N10" t="s">
+      <c r="N10" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="O10" t="s">
+      <c r="O10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="Q10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="R10" t="s">
+      <c r="R10" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="S10" t="s">
+      <c r="S10" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="T10" t="s">
+      <c r="T10" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B11" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" t="s">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="B11" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G11" t="s">
-        <v>88</v>
-      </c>
-      <c r="H11" t="s">
-        <v>210</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="E11" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="J11" t="s">
+      <c r="I11" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="L11" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="J11" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N11" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="O11" t="s">
+      <c r="O11" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="T11" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="B12" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q12" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="R12" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="S12" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="T12" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="B13" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="S13" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="T13" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="B14" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q14" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="R14" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="S14" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="T14" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="B15" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="T15" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="B16" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q16" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="R16" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="S16" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="T16" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="T17" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B18" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q18" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="R18" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="S18" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="T18" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B19" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="T19" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B20" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="I20" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="Q11" t="s">
-        <v>88</v>
-      </c>
-      <c r="R11" t="s">
+      <c r="J20" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q20" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="R20" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="S20" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="T20" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B21" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="S21" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="T21" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B22" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q22" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="R22" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="S22" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="T22" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B23" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R23" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="S23" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="T23" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B24" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q24" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="S24" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="T24" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B25" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="R25" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="S25" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="T25" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B26" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="O26" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q26" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="R26" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="S26" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="T26" s="8" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B27" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B28" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="O28" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B29" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="O29" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B30" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M30" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="O30" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B31" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="O31" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B32" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M32" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="N32" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="O32" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B33" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="O33" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B34" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="N34" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="O34" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B35" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="O35" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B36" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="N36" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="O36" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B37" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M37" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="O37" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B38" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M38" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="N38" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="O38" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B39" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M39" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="O39" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B40" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M40" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="N40" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="O40" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B41" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="O41" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B42" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M42" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="N42" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="O42" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B43" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M43" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="N43" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="O43" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B44" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M44" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="N44" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="O44" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B45" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M45" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="N45" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="O45" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B46" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M46" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="N46" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="O46" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B47" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M47" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="N47" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="O47" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B48" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M48" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="N48" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="O48" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B49" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M49" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="N49" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="O49" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B50" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M50" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="N50" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="O50" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B51" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M51" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="N51" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="O51" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="52" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B52" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M52" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="N52" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="O52" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="53" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B53" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M53" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="N53" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="O53" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B54" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="N54" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="O54" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="55" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B55" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L55" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M55" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="N55" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="O55" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="56" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B56" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="N56" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="O56" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="57" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B57" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L57" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M57" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="N57" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="O57" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="58" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B58" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M58" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="N58" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="O58" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="59" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B59" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L59" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M59" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="N59" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="O59" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="60" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B60" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L60" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M60" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="N60" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="O60" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="61" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B61" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L61" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M61" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="N61" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="O61" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="62" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B62" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L62" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M62" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="N62" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="O62" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="63" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B63" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M63" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="N63" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="O63" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="64" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B64" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L64" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M64" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="N64" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="O64" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B65" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L65" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M65" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="N65" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="O65" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B66" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L66" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M66" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="N66" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="O66" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B67" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L67" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M67" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="N67" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="O67" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B68" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="E68" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L68" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M68" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="N68" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="O68" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B69" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="L69" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M69" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="N69" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="O69" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B70" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E70" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="L70" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M70" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="N70" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="O70" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="L71" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M71" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="N71" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="O71" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="L72" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M72" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="N72" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="O72" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="L73" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M73" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="N73" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="O73" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="L74" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M74" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="N74" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="O74" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="L75" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M75" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="N75" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="S11" t="s">
-        <v>237</v>
-      </c>
-      <c r="T11" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" t="s">
-        <v>91</v>
-      </c>
-      <c r="G12" t="s">
-        <v>88</v>
-      </c>
-      <c r="H12" t="s">
-        <v>213</v>
-      </c>
-      <c r="I12" t="s">
-        <v>214</v>
-      </c>
-      <c r="J12" t="s">
-        <v>212</v>
-      </c>
-      <c r="L12" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" t="s">
-        <v>92</v>
-      </c>
-      <c r="N12" t="s">
-        <v>93</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="O75" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="L76" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M76" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="N76" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="O76" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="L77" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M77" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="N77" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="O77" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="78" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="L78" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M78" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="N78" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="O78" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="L79" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M79" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="N79" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="O79" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="80" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="L80" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M80" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="N80" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="Q12" t="s">
-        <v>88</v>
-      </c>
-      <c r="R12" t="s">
-        <v>239</v>
-      </c>
-      <c r="S12" t="s">
-        <v>240</v>
-      </c>
-      <c r="T12" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" t="s">
-        <v>91</v>
-      </c>
-      <c r="G13" t="s">
-        <v>88</v>
-      </c>
-      <c r="H13" t="s">
-        <v>215</v>
-      </c>
-      <c r="I13" t="s">
-        <v>216</v>
-      </c>
-      <c r="J13" t="s">
-        <v>212</v>
-      </c>
-      <c r="L13" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" t="s">
-        <v>94</v>
-      </c>
-      <c r="N13" t="s">
-        <v>95</v>
-      </c>
-      <c r="O13" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>88</v>
-      </c>
-      <c r="R13" t="s">
-        <v>106</v>
-      </c>
-      <c r="S13" t="s">
-        <v>107</v>
-      </c>
-      <c r="T13" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B14" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" t="s">
-        <v>91</v>
-      </c>
-      <c r="G14" t="s">
-        <v>88</v>
-      </c>
-      <c r="H14" t="s">
-        <v>217</v>
-      </c>
-      <c r="I14" t="s">
-        <v>218</v>
-      </c>
-      <c r="J14" t="s">
-        <v>212</v>
-      </c>
-      <c r="L14" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14" t="s">
-        <v>96</v>
-      </c>
-      <c r="N14" t="s">
-        <v>97</v>
-      </c>
-      <c r="O14" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>88</v>
-      </c>
-      <c r="R14" t="s">
-        <v>128</v>
-      </c>
-      <c r="S14" t="s">
-        <v>129</v>
-      </c>
-      <c r="T14" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" t="s">
-        <v>91</v>
-      </c>
-      <c r="G15" t="s">
-        <v>88</v>
-      </c>
-      <c r="H15" t="s">
-        <v>219</v>
-      </c>
-      <c r="I15" t="s">
-        <v>220</v>
-      </c>
-      <c r="J15" t="s">
-        <v>212</v>
-      </c>
-      <c r="L15" t="s">
-        <v>88</v>
-      </c>
-      <c r="M15" t="s">
-        <v>98</v>
-      </c>
-      <c r="N15" t="s">
-        <v>99</v>
-      </c>
-      <c r="O15" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>88</v>
-      </c>
-      <c r="R15" t="s">
-        <v>241</v>
-      </c>
-      <c r="S15" t="s">
-        <v>242</v>
-      </c>
-      <c r="T15" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" t="s">
-        <v>91</v>
-      </c>
-      <c r="G16" t="s">
-        <v>88</v>
-      </c>
-      <c r="H16" t="s">
-        <v>221</v>
-      </c>
-      <c r="I16" t="s">
-        <v>222</v>
-      </c>
-      <c r="J16" t="s">
-        <v>212</v>
-      </c>
-      <c r="L16" t="s">
-        <v>88</v>
-      </c>
-      <c r="M16" t="s">
-        <v>100</v>
-      </c>
-      <c r="N16" t="s">
-        <v>101</v>
-      </c>
-      <c r="O16" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>88</v>
-      </c>
-      <c r="R16" t="s">
-        <v>243</v>
-      </c>
-      <c r="S16" t="s">
-        <v>244</v>
-      </c>
-      <c r="T16" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B17" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" t="s">
-        <v>91</v>
-      </c>
-      <c r="G17" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" t="s">
-        <v>178</v>
-      </c>
-      <c r="I17" t="s">
-        <v>179</v>
-      </c>
-      <c r="J17" t="s">
-        <v>212</v>
-      </c>
-      <c r="L17" t="s">
-        <v>88</v>
-      </c>
-      <c r="M17" t="s">
-        <v>102</v>
-      </c>
-      <c r="N17" t="s">
-        <v>103</v>
-      </c>
-      <c r="O17" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>88</v>
-      </c>
-      <c r="R17" t="s">
-        <v>140</v>
-      </c>
-      <c r="S17" t="s">
-        <v>141</v>
-      </c>
-      <c r="T17" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B18" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" t="s">
-        <v>91</v>
-      </c>
-      <c r="G18" t="s">
-        <v>88</v>
-      </c>
-      <c r="H18" t="s">
-        <v>192</v>
-      </c>
-      <c r="I18" t="s">
-        <v>193</v>
-      </c>
-      <c r="J18" t="s">
-        <v>212</v>
-      </c>
-      <c r="L18" t="s">
-        <v>88</v>
-      </c>
-      <c r="M18" t="s">
-        <v>104</v>
-      </c>
-      <c r="N18" t="s">
-        <v>105</v>
-      </c>
-      <c r="O18" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>88</v>
-      </c>
-      <c r="R18" t="s">
-        <v>245</v>
-      </c>
-      <c r="S18" t="s">
-        <v>246</v>
-      </c>
-      <c r="T18" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" t="s">
-        <v>91</v>
-      </c>
-      <c r="G19" t="s">
-        <v>88</v>
-      </c>
-      <c r="H19" t="s">
-        <v>223</v>
-      </c>
-      <c r="I19" t="s">
-        <v>224</v>
-      </c>
-      <c r="J19" t="s">
-        <v>212</v>
-      </c>
-      <c r="L19" t="s">
-        <v>88</v>
-      </c>
-      <c r="M19" t="s">
-        <v>106</v>
-      </c>
-      <c r="N19" t="s">
-        <v>107</v>
-      </c>
-      <c r="O19" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>88</v>
-      </c>
-      <c r="R19" t="s">
-        <v>247</v>
-      </c>
-      <c r="S19" t="s">
-        <v>248</v>
-      </c>
-      <c r="T19" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" t="s">
-        <v>91</v>
-      </c>
-      <c r="G20" t="s">
-        <v>88</v>
-      </c>
-      <c r="H20" t="s">
-        <v>225</v>
-      </c>
-      <c r="I20" t="s">
-        <v>226</v>
-      </c>
-      <c r="J20" t="s">
-        <v>212</v>
-      </c>
-      <c r="L20" t="s">
-        <v>88</v>
-      </c>
-      <c r="M20" t="s">
-        <v>108</v>
-      </c>
-      <c r="N20" t="s">
-        <v>109</v>
-      </c>
-      <c r="O20" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>88</v>
-      </c>
-      <c r="R20" t="s">
-        <v>249</v>
-      </c>
-      <c r="S20" t="s">
-        <v>250</v>
-      </c>
-      <c r="T20" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B21" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" t="s">
-        <v>111</v>
-      </c>
-      <c r="E21" t="s">
-        <v>91</v>
-      </c>
-      <c r="L21" t="s">
-        <v>88</v>
-      </c>
-      <c r="M21" t="s">
-        <v>110</v>
-      </c>
-      <c r="N21" t="s">
-        <v>111</v>
-      </c>
-      <c r="O21" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>88</v>
-      </c>
-      <c r="R21" t="s">
-        <v>251</v>
-      </c>
-      <c r="S21" t="s">
-        <v>252</v>
-      </c>
-      <c r="T21" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" t="s">
-        <v>112</v>
-      </c>
-      <c r="D22" t="s">
-        <v>113</v>
-      </c>
-      <c r="E22" t="s">
-        <v>91</v>
-      </c>
-      <c r="L22" t="s">
-        <v>88</v>
-      </c>
-      <c r="M22" t="s">
-        <v>112</v>
-      </c>
-      <c r="N22" t="s">
-        <v>113</v>
-      </c>
-      <c r="O22" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>88</v>
-      </c>
-      <c r="R22" t="s">
-        <v>94</v>
-      </c>
-      <c r="S22" t="s">
-        <v>95</v>
-      </c>
-      <c r="T22" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" t="s">
-        <v>91</v>
-      </c>
-      <c r="L23" t="s">
-        <v>88</v>
-      </c>
-      <c r="M23" t="s">
-        <v>114</v>
-      </c>
-      <c r="N23" t="s">
-        <v>115</v>
-      </c>
-      <c r="O23" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>88</v>
-      </c>
-      <c r="R23" t="s">
-        <v>253</v>
-      </c>
-      <c r="S23" t="s">
-        <v>254</v>
-      </c>
-      <c r="T23" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B24" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" t="s">
-        <v>117</v>
-      </c>
-      <c r="E24" t="s">
-        <v>91</v>
-      </c>
-      <c r="L24" t="s">
-        <v>88</v>
-      </c>
-      <c r="M24" t="s">
-        <v>116</v>
-      </c>
-      <c r="N24" t="s">
-        <v>117</v>
-      </c>
-      <c r="O24" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>88</v>
-      </c>
-      <c r="R24" t="s">
-        <v>166</v>
-      </c>
-      <c r="S24" t="s">
-        <v>167</v>
-      </c>
-      <c r="T24" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B25" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" t="s">
-        <v>119</v>
-      </c>
-      <c r="E25" t="s">
-        <v>91</v>
-      </c>
-      <c r="L25" t="s">
-        <v>88</v>
-      </c>
-      <c r="M25" t="s">
-        <v>118</v>
-      </c>
-      <c r="N25" t="s">
-        <v>119</v>
-      </c>
-      <c r="O25" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>88</v>
-      </c>
-      <c r="R25" t="s">
-        <v>255</v>
-      </c>
-      <c r="S25" t="s">
-        <v>256</v>
-      </c>
-      <c r="T25" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" t="s">
-        <v>121</v>
-      </c>
-      <c r="E26" t="s">
-        <v>91</v>
-      </c>
-      <c r="L26" t="s">
-        <v>88</v>
-      </c>
-      <c r="M26" t="s">
-        <v>120</v>
-      </c>
-      <c r="N26" t="s">
-        <v>121</v>
-      </c>
-      <c r="O26" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>88</v>
-      </c>
-      <c r="R26" t="s">
-        <v>223</v>
-      </c>
-      <c r="S26" t="s">
-        <v>224</v>
-      </c>
-      <c r="T26" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s">
-        <v>122</v>
-      </c>
-      <c r="D27" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" t="s">
-        <v>91</v>
-      </c>
-      <c r="L27" t="s">
-        <v>88</v>
-      </c>
-      <c r="M27" t="s">
-        <v>122</v>
-      </c>
-      <c r="N27" t="s">
-        <v>123</v>
-      </c>
-      <c r="O27" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" t="s">
-        <v>125</v>
-      </c>
-      <c r="E28" t="s">
-        <v>91</v>
-      </c>
-      <c r="L28" t="s">
-        <v>88</v>
-      </c>
-      <c r="M28" t="s">
-        <v>124</v>
-      </c>
-      <c r="N28" t="s">
-        <v>125</v>
-      </c>
-      <c r="O28" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B29" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" t="s">
-        <v>127</v>
-      </c>
-      <c r="E29" t="s">
-        <v>91</v>
-      </c>
-      <c r="L29" t="s">
-        <v>88</v>
-      </c>
-      <c r="M29" t="s">
-        <v>126</v>
-      </c>
-      <c r="N29" t="s">
-        <v>127</v>
-      </c>
-      <c r="O29" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" t="s">
-        <v>129</v>
-      </c>
-      <c r="E30" t="s">
-        <v>91</v>
-      </c>
-      <c r="L30" t="s">
-        <v>88</v>
-      </c>
-      <c r="M30" t="s">
-        <v>128</v>
-      </c>
-      <c r="N30" t="s">
-        <v>129</v>
-      </c>
-      <c r="O30" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B31" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" t="s">
-        <v>131</v>
-      </c>
-      <c r="E31" t="s">
-        <v>91</v>
-      </c>
-      <c r="L31" t="s">
-        <v>88</v>
-      </c>
-      <c r="M31" t="s">
-        <v>130</v>
-      </c>
-      <c r="N31" t="s">
-        <v>131</v>
-      </c>
-      <c r="O31" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="B32" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" t="s">
-        <v>133</v>
-      </c>
-      <c r="E32" t="s">
-        <v>91</v>
-      </c>
-      <c r="L32" t="s">
-        <v>88</v>
-      </c>
-      <c r="M32" t="s">
-        <v>132</v>
-      </c>
-      <c r="N32" t="s">
-        <v>133</v>
-      </c>
-      <c r="O32" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B33" t="s">
-        <v>88</v>
-      </c>
-      <c r="C33" t="s">
-        <v>134</v>
-      </c>
-      <c r="D33" t="s">
-        <v>135</v>
-      </c>
-      <c r="E33" t="s">
-        <v>91</v>
-      </c>
-      <c r="L33" t="s">
-        <v>88</v>
-      </c>
-      <c r="M33" t="s">
-        <v>134</v>
-      </c>
-      <c r="N33" t="s">
-        <v>135</v>
-      </c>
-      <c r="O33" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B34" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" t="s">
-        <v>136</v>
-      </c>
-      <c r="D34" t="s">
-        <v>137</v>
-      </c>
-      <c r="E34" t="s">
-        <v>91</v>
-      </c>
-      <c r="L34" t="s">
-        <v>88</v>
-      </c>
-      <c r="M34" t="s">
-        <v>136</v>
-      </c>
-      <c r="N34" t="s">
-        <v>137</v>
-      </c>
-      <c r="O34" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B35" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" t="s">
-        <v>138</v>
-      </c>
-      <c r="D35" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" t="s">
-        <v>91</v>
-      </c>
-      <c r="L35" t="s">
-        <v>88</v>
-      </c>
-      <c r="M35" t="s">
-        <v>138</v>
-      </c>
-      <c r="N35" t="s">
-        <v>139</v>
-      </c>
-      <c r="O35" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B36" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" t="s">
-        <v>140</v>
-      </c>
-      <c r="D36" t="s">
-        <v>141</v>
-      </c>
-      <c r="E36" t="s">
-        <v>91</v>
-      </c>
-      <c r="L36" t="s">
-        <v>88</v>
-      </c>
-      <c r="M36" t="s">
-        <v>140</v>
-      </c>
-      <c r="N36" t="s">
-        <v>141</v>
-      </c>
-      <c r="O36" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B37" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" t="s">
-        <v>142</v>
-      </c>
-      <c r="D37" t="s">
-        <v>143</v>
-      </c>
-      <c r="E37" t="s">
-        <v>91</v>
-      </c>
-      <c r="L37" t="s">
-        <v>88</v>
-      </c>
-      <c r="M37" t="s">
-        <v>142</v>
-      </c>
-      <c r="N37" t="s">
-        <v>143</v>
-      </c>
-      <c r="O37" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B38" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" t="s">
-        <v>144</v>
-      </c>
-      <c r="D38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E38" t="s">
-        <v>91</v>
-      </c>
-      <c r="L38" t="s">
-        <v>88</v>
-      </c>
-      <c r="M38" t="s">
-        <v>144</v>
-      </c>
-      <c r="N38" t="s">
-        <v>145</v>
-      </c>
-      <c r="O38" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B39" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" t="s">
-        <v>146</v>
-      </c>
-      <c r="D39" t="s">
-        <v>147</v>
-      </c>
-      <c r="E39" t="s">
-        <v>91</v>
-      </c>
-      <c r="L39" t="s">
-        <v>88</v>
-      </c>
-      <c r="M39" t="s">
-        <v>146</v>
-      </c>
-      <c r="N39" t="s">
-        <v>147</v>
-      </c>
-      <c r="O39" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" t="s">
-        <v>148</v>
-      </c>
-      <c r="D40" t="s">
-        <v>149</v>
-      </c>
-      <c r="E40" t="s">
-        <v>91</v>
-      </c>
-      <c r="L40" t="s">
-        <v>88</v>
-      </c>
-      <c r="M40" t="s">
-        <v>148</v>
-      </c>
-      <c r="N40" t="s">
-        <v>149</v>
-      </c>
-      <c r="O40" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B41" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" t="s">
-        <v>150</v>
-      </c>
-      <c r="D41" t="s">
-        <v>151</v>
-      </c>
-      <c r="E41" t="s">
-        <v>91</v>
-      </c>
-      <c r="L41" t="s">
-        <v>88</v>
-      </c>
-      <c r="M41" t="s">
-        <v>150</v>
-      </c>
-      <c r="N41" t="s">
-        <v>151</v>
-      </c>
-      <c r="O41" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" t="s">
-        <v>152</v>
-      </c>
-      <c r="D42" t="s">
-        <v>153</v>
-      </c>
-      <c r="E42" t="s">
-        <v>91</v>
-      </c>
-      <c r="L42" t="s">
-        <v>88</v>
-      </c>
-      <c r="M42" t="s">
-        <v>152</v>
-      </c>
-      <c r="N42" t="s">
-        <v>153</v>
-      </c>
-      <c r="O42" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B43" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" t="s">
-        <v>154</v>
-      </c>
-      <c r="D43" t="s">
-        <v>155</v>
-      </c>
-      <c r="E43" t="s">
-        <v>91</v>
-      </c>
-      <c r="L43" t="s">
-        <v>88</v>
-      </c>
-      <c r="M43" t="s">
-        <v>154</v>
-      </c>
-      <c r="N43" t="s">
-        <v>155</v>
-      </c>
-      <c r="O43" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B44" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" t="s">
-        <v>156</v>
-      </c>
-      <c r="D44" t="s">
-        <v>157</v>
-      </c>
-      <c r="E44" t="s">
-        <v>91</v>
-      </c>
-      <c r="L44" t="s">
-        <v>88</v>
-      </c>
-      <c r="M44" t="s">
-        <v>156</v>
-      </c>
-      <c r="N44" t="s">
-        <v>157</v>
-      </c>
-      <c r="O44" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" t="s">
-        <v>158</v>
-      </c>
-      <c r="D45" t="s">
-        <v>159</v>
-      </c>
-      <c r="E45" t="s">
-        <v>91</v>
-      </c>
-      <c r="L45" t="s">
-        <v>88</v>
-      </c>
-      <c r="M45" t="s">
-        <v>158</v>
-      </c>
-      <c r="N45" t="s">
-        <v>159</v>
-      </c>
-      <c r="O45" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B46" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" t="s">
-        <v>160</v>
-      </c>
-      <c r="D46" t="s">
-        <v>161</v>
-      </c>
-      <c r="E46" t="s">
-        <v>91</v>
-      </c>
-      <c r="L46" t="s">
-        <v>88</v>
-      </c>
-      <c r="M46" t="s">
-        <v>160</v>
-      </c>
-      <c r="N46" t="s">
-        <v>161</v>
-      </c>
-      <c r="O46" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C47" t="s">
-        <v>162</v>
-      </c>
-      <c r="D47" t="s">
-        <v>163</v>
-      </c>
-      <c r="E47" t="s">
-        <v>91</v>
-      </c>
-      <c r="L47" t="s">
-        <v>88</v>
-      </c>
-      <c r="M47" t="s">
-        <v>162</v>
-      </c>
-      <c r="N47" t="s">
-        <v>163</v>
-      </c>
-      <c r="O47" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B48" t="s">
-        <v>88</v>
-      </c>
-      <c r="C48" t="s">
-        <v>164</v>
-      </c>
-      <c r="D48" t="s">
-        <v>165</v>
-      </c>
-      <c r="E48" t="s">
-        <v>91</v>
-      </c>
-      <c r="L48" t="s">
-        <v>88</v>
-      </c>
-      <c r="M48" t="s">
-        <v>164</v>
-      </c>
-      <c r="N48" t="s">
-        <v>165</v>
-      </c>
-      <c r="O48" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" t="s">
-        <v>166</v>
-      </c>
-      <c r="D49" t="s">
-        <v>167</v>
-      </c>
-      <c r="E49" t="s">
-        <v>91</v>
-      </c>
-      <c r="L49" t="s">
-        <v>88</v>
-      </c>
-      <c r="M49" t="s">
-        <v>166</v>
-      </c>
-      <c r="N49" t="s">
-        <v>167</v>
-      </c>
-      <c r="O49" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B50" t="s">
-        <v>88</v>
-      </c>
-      <c r="C50" t="s">
-        <v>168</v>
-      </c>
-      <c r="D50" t="s">
-        <v>169</v>
-      </c>
-      <c r="E50" t="s">
-        <v>91</v>
-      </c>
-      <c r="L50" t="s">
-        <v>88</v>
-      </c>
-      <c r="M50" t="s">
-        <v>168</v>
-      </c>
-      <c r="N50" t="s">
-        <v>169</v>
-      </c>
-      <c r="O50" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" t="s">
-        <v>170</v>
-      </c>
-      <c r="D51" t="s">
-        <v>171</v>
-      </c>
-      <c r="E51" t="s">
-        <v>91</v>
-      </c>
-      <c r="L51" t="s">
-        <v>88</v>
-      </c>
-      <c r="M51" t="s">
-        <v>170</v>
-      </c>
-      <c r="N51" t="s">
-        <v>171</v>
-      </c>
-      <c r="O51" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B52" t="s">
-        <v>88</v>
-      </c>
-      <c r="C52" t="s">
-        <v>172</v>
-      </c>
-      <c r="D52" t="s">
-        <v>173</v>
-      </c>
-      <c r="E52" t="s">
-        <v>91</v>
-      </c>
-      <c r="L52" t="s">
-        <v>88</v>
-      </c>
-      <c r="M52" t="s">
-        <v>172</v>
-      </c>
-      <c r="N52" t="s">
-        <v>173</v>
-      </c>
-      <c r="O52" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B53" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" t="s">
-        <v>174</v>
-      </c>
-      <c r="D53" t="s">
-        <v>175</v>
-      </c>
-      <c r="E53" t="s">
-        <v>91</v>
-      </c>
-      <c r="L53" t="s">
-        <v>88</v>
-      </c>
-      <c r="M53" t="s">
-        <v>174</v>
-      </c>
-      <c r="N53" t="s">
-        <v>175</v>
-      </c>
-      <c r="O53" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B54" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" t="s">
-        <v>176</v>
-      </c>
-      <c r="D54" t="s">
-        <v>177</v>
-      </c>
-      <c r="E54" t="s">
-        <v>91</v>
-      </c>
-      <c r="L54" t="s">
-        <v>88</v>
-      </c>
-      <c r="M54" t="s">
-        <v>176</v>
-      </c>
-      <c r="N54" t="s">
-        <v>177</v>
-      </c>
-      <c r="O54" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B55" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" t="s">
-        <v>178</v>
-      </c>
-      <c r="D55" t="s">
-        <v>179</v>
-      </c>
-      <c r="E55" t="s">
-        <v>91</v>
-      </c>
-      <c r="L55" t="s">
-        <v>88</v>
-      </c>
-      <c r="M55" t="s">
-        <v>178</v>
-      </c>
-      <c r="N55" t="s">
-        <v>179</v>
-      </c>
-      <c r="O55" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B56" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" t="s">
-        <v>180</v>
-      </c>
-      <c r="D56" t="s">
-        <v>181</v>
-      </c>
-      <c r="E56" t="s">
-        <v>91</v>
-      </c>
-      <c r="L56" t="s">
-        <v>88</v>
-      </c>
-      <c r="M56" t="s">
-        <v>180</v>
-      </c>
-      <c r="N56" t="s">
-        <v>181</v>
-      </c>
-      <c r="O56" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="57" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B57" t="s">
-        <v>88</v>
-      </c>
-      <c r="C57" t="s">
-        <v>182</v>
-      </c>
-      <c r="D57" t="s">
-        <v>183</v>
-      </c>
-      <c r="E57" t="s">
-        <v>91</v>
-      </c>
-      <c r="L57" t="s">
-        <v>88</v>
-      </c>
-      <c r="M57" t="s">
-        <v>182</v>
-      </c>
-      <c r="N57" t="s">
-        <v>183</v>
-      </c>
-      <c r="O57" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B58" t="s">
-        <v>88</v>
-      </c>
-      <c r="C58" t="s">
-        <v>184</v>
-      </c>
-      <c r="D58" t="s">
-        <v>185</v>
-      </c>
-      <c r="E58" t="s">
-        <v>91</v>
-      </c>
-      <c r="L58" t="s">
-        <v>88</v>
-      </c>
-      <c r="M58" t="s">
-        <v>184</v>
-      </c>
-      <c r="N58" t="s">
-        <v>185</v>
-      </c>
-      <c r="O58" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B59" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59" t="s">
-        <v>186</v>
-      </c>
-      <c r="D59" t="s">
-        <v>187</v>
-      </c>
-      <c r="E59" t="s">
-        <v>91</v>
-      </c>
-      <c r="L59" t="s">
-        <v>88</v>
-      </c>
-      <c r="M59" t="s">
-        <v>186</v>
-      </c>
-      <c r="N59" t="s">
-        <v>187</v>
-      </c>
-      <c r="O59" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B60" t="s">
-        <v>88</v>
-      </c>
-      <c r="C60" t="s">
-        <v>188</v>
-      </c>
-      <c r="D60" t="s">
-        <v>189</v>
-      </c>
-      <c r="E60" t="s">
-        <v>91</v>
-      </c>
-      <c r="L60" t="s">
-        <v>88</v>
-      </c>
-      <c r="M60" t="s">
-        <v>188</v>
-      </c>
-      <c r="N60" t="s">
-        <v>189</v>
-      </c>
-      <c r="O60" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B61" t="s">
-        <v>88</v>
-      </c>
-      <c r="C61" t="s">
-        <v>190</v>
-      </c>
-      <c r="D61" t="s">
-        <v>191</v>
-      </c>
-      <c r="E61" t="s">
-        <v>91</v>
-      </c>
-      <c r="L61" t="s">
-        <v>88</v>
-      </c>
-      <c r="M61" t="s">
-        <v>190</v>
-      </c>
-      <c r="N61" t="s">
-        <v>191</v>
-      </c>
-      <c r="O61" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B62" t="s">
-        <v>88</v>
-      </c>
-      <c r="C62" t="s">
-        <v>192</v>
-      </c>
-      <c r="D62" t="s">
-        <v>193</v>
-      </c>
-      <c r="E62" t="s">
-        <v>91</v>
-      </c>
-      <c r="L62" t="s">
-        <v>88</v>
-      </c>
-      <c r="M62" t="s">
-        <v>192</v>
-      </c>
-      <c r="N62" t="s">
-        <v>193</v>
-      </c>
-      <c r="O62" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B63" t="s">
-        <v>88</v>
-      </c>
-      <c r="C63" t="s">
-        <v>194</v>
-      </c>
-      <c r="D63" t="s">
-        <v>195</v>
-      </c>
-      <c r="E63" t="s">
-        <v>91</v>
-      </c>
-      <c r="L63" t="s">
-        <v>88</v>
-      </c>
-      <c r="M63" t="s">
-        <v>194</v>
-      </c>
-      <c r="N63" t="s">
-        <v>195</v>
-      </c>
-      <c r="O63" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B64" t="s">
-        <v>88</v>
-      </c>
-      <c r="C64" t="s">
-        <v>196</v>
-      </c>
-      <c r="D64" t="s">
-        <v>197</v>
-      </c>
-      <c r="E64" t="s">
-        <v>91</v>
-      </c>
-      <c r="L64" t="s">
-        <v>88</v>
-      </c>
-      <c r="M64" t="s">
-        <v>210</v>
-      </c>
-      <c r="N64" t="s">
-        <v>211</v>
-      </c>
-      <c r="O64" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B65" t="s">
-        <v>88</v>
-      </c>
-      <c r="C65" t="s">
-        <v>198</v>
-      </c>
-      <c r="D65" t="s">
-        <v>199</v>
-      </c>
-      <c r="E65" t="s">
-        <v>91</v>
-      </c>
-      <c r="L65" t="s">
-        <v>88</v>
-      </c>
-      <c r="M65" t="s">
-        <v>213</v>
-      </c>
-      <c r="N65" t="s">
-        <v>214</v>
-      </c>
-      <c r="O65" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B66" t="s">
-        <v>88</v>
-      </c>
-      <c r="C66" t="s">
-        <v>200</v>
-      </c>
-      <c r="D66" t="s">
-        <v>201</v>
-      </c>
-      <c r="E66" t="s">
-        <v>91</v>
-      </c>
-      <c r="L66" t="s">
-        <v>88</v>
-      </c>
-      <c r="M66" t="s">
-        <v>215</v>
-      </c>
-      <c r="N66" t="s">
-        <v>216</v>
-      </c>
-      <c r="O66" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B67" t="s">
-        <v>88</v>
-      </c>
-      <c r="C67" t="s">
-        <v>202</v>
-      </c>
-      <c r="D67" t="s">
-        <v>203</v>
-      </c>
-      <c r="E67" t="s">
-        <v>91</v>
-      </c>
-      <c r="L67" t="s">
-        <v>88</v>
-      </c>
-      <c r="M67" t="s">
-        <v>217</v>
-      </c>
-      <c r="N67" t="s">
-        <v>218</v>
-      </c>
-      <c r="O67" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B68" t="s">
-        <v>88</v>
-      </c>
-      <c r="C68" t="s">
-        <v>204</v>
-      </c>
-      <c r="D68" t="s">
-        <v>205</v>
-      </c>
-      <c r="E68" t="s">
-        <v>91</v>
-      </c>
-      <c r="L68" t="s">
-        <v>88</v>
-      </c>
-      <c r="M68" t="s">
-        <v>219</v>
-      </c>
-      <c r="N68" t="s">
-        <v>220</v>
-      </c>
-      <c r="O68" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B69" t="s">
-        <v>88</v>
-      </c>
-      <c r="C69" t="s">
+      <c r="O80" s="8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="81" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L81" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="M81" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="D69" t="s">
+      <c r="N81" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="E69" t="s">
-        <v>91</v>
-      </c>
-      <c r="L69" t="s">
-        <v>88</v>
-      </c>
-      <c r="M69" t="s">
-        <v>221</v>
-      </c>
-      <c r="N69" t="s">
-        <v>222</v>
-      </c>
-      <c r="O69" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B70" t="s">
-        <v>88</v>
-      </c>
-      <c r="C70" t="s">
+      <c r="O81" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="82" spans="12:15" x14ac:dyDescent="0.45">
+      <c r="L82" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M82" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="D70" t="s">
+      <c r="N82" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="E70" t="s">
-        <v>91</v>
-      </c>
-      <c r="L70" t="s">
-        <v>88</v>
-      </c>
-      <c r="M70" t="s">
-        <v>223</v>
-      </c>
-      <c r="N70" t="s">
-        <v>224</v>
-      </c>
-      <c r="O70" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L71" t="s">
-        <v>88</v>
-      </c>
-      <c r="M71" t="s">
-        <v>228</v>
-      </c>
-      <c r="N71" t="s">
-        <v>229</v>
-      </c>
-      <c r="O71" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L72" t="s">
-        <v>88</v>
-      </c>
-      <c r="M72" t="s">
-        <v>230</v>
-      </c>
-      <c r="N72" t="s">
-        <v>231</v>
-      </c>
-      <c r="O72" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L73" t="s">
-        <v>88</v>
-      </c>
-      <c r="M73" t="s">
-        <v>232</v>
-      </c>
-      <c r="N73" t="s">
-        <v>233</v>
-      </c>
-      <c r="O73" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L74" t="s">
-        <v>88</v>
-      </c>
-      <c r="M74" t="s">
-        <v>196</v>
-      </c>
-      <c r="N74" t="s">
-        <v>197</v>
-      </c>
-      <c r="O74" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L75" t="s">
-        <v>88</v>
-      </c>
-      <c r="M75" t="s">
-        <v>234</v>
-      </c>
-      <c r="N75" t="s">
-        <v>235</v>
-      </c>
-      <c r="O75" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L76" t="s">
-        <v>88</v>
-      </c>
-      <c r="M76" t="s">
-        <v>198</v>
-      </c>
-      <c r="N76" t="s">
-        <v>199</v>
-      </c>
-      <c r="O76" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L77" t="s">
-        <v>88</v>
-      </c>
-      <c r="M77" t="s">
-        <v>200</v>
-      </c>
-      <c r="N77" t="s">
-        <v>201</v>
-      </c>
-      <c r="O77" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="78" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L78" t="s">
-        <v>88</v>
-      </c>
-      <c r="M78" t="s">
-        <v>202</v>
-      </c>
-      <c r="N78" t="s">
-        <v>203</v>
-      </c>
-      <c r="O78" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L79" t="s">
-        <v>88</v>
-      </c>
-      <c r="M79" t="s">
-        <v>204</v>
-      </c>
-      <c r="N79" t="s">
-        <v>205</v>
-      </c>
-      <c r="O79" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L80" t="s">
-        <v>88</v>
-      </c>
-      <c r="M80" t="s">
-        <v>225</v>
-      </c>
-      <c r="N80" t="s">
-        <v>226</v>
-      </c>
-      <c r="O80" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="81" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L81" t="s">
-        <v>88</v>
-      </c>
-      <c r="M81" t="s">
-        <v>206</v>
-      </c>
-      <c r="N81" t="s">
-        <v>207</v>
-      </c>
-      <c r="O81" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="82" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L82" t="s">
-        <v>88</v>
-      </c>
-      <c r="M82" t="s">
-        <v>208</v>
-      </c>
-      <c r="N82" t="s">
-        <v>209</v>
-      </c>
-      <c r="O82" t="s">
-        <v>227</v>
+      <c r="O82" s="8" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D2C9E1F-217F-45F9-A10A-2FC97388DDA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{885E1FFF-B243-4D54-B3DA-6B5004A54BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="257">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -313,7 +313,7 @@
     <t>at grid node - w66161634-220_POL</t>
   </si>
   <si>
-    <t>Bioenergy + CCUS,Bioenergy - Large scale unit,CCGT,CCGT + CCS,Coal + CCS,Gas turbine,IGCC,IGCC + CCS,Nuclear large,Oxyfuel + CCS,Steam Coal - SUBCRITICAL,Steam Coal - SUPERCRITICAL,Steam Coal - ULTRASUPERCRITICAL</t>
+    <t>en_gas_ccgt,en_gas_turbine,en_gas_chp,en_gas_fuelcell,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_coal_ccs,en_coal_igcc_ccs,en_coal_oxyfuel_ccs,en_nuclear,en_nuclear_smr,en_biomass,en_biomass_cofiring,en_biomass_chp,en_biomass_ccs,en_geothermal</t>
   </si>
   <si>
     <t>w681264796-400_POL</t>
@@ -673,15 +673,15 @@
     <t>VERVESTACKS - the open USE platform · Powered by data · Shaped by vision · Guided by intuition · Fueled by passion</t>
   </si>
   <si>
+    <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
+  </si>
+  <si>
     <t>w158232924-220_POL</t>
   </si>
   <si>
     <t>at grid node - w158232924-220_POL</t>
   </si>
   <si>
-    <t>EN_Hydro_POL-1,EN_Hydro_POL-2,EN_Hydro_POL-3</t>
-  </si>
-  <si>
     <t>w179279860-220_POL</t>
   </si>
   <si>
@@ -718,37 +718,34 @@
     <t>at grid node - w178838661-220_POL</t>
   </si>
   <si>
+    <t>w255314292_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w255314292_POL</t>
+  </si>
+  <si>
+    <t>w185459155-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w185459155-220_POL</t>
+  </si>
+  <si>
+    <t>w336990960-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w336990960-220_POL</t>
+  </si>
+  <si>
+    <t>w175406958-220_POL</t>
+  </si>
+  <si>
+    <t>at grid node - w175406958-220_POL</t>
+  </si>
+  <si>
     <t>w166710856-400_POL</t>
   </si>
   <si>
     <t>at grid node - w166710856-400_POL</t>
-  </si>
-  <si>
-    <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
-  </si>
-  <si>
-    <t>w255314292_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w255314292_POL</t>
-  </si>
-  <si>
-    <t>w185459155-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w185459155-220_POL</t>
-  </si>
-  <si>
-    <t>w336990960-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w336990960-220_POL</t>
-  </si>
-  <si>
-    <t>w175406958-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w175406958-220_POL</t>
   </si>
   <si>
     <t>PL58-220_POL</t>
@@ -978,7 +975,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AFB8134-C140-0F24-F697-C8186D73AF0F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD170467-8275-13C1-A7A8-239E979325B4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1276,7 +1273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="A1:T82"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="10.59765625" customWidth="1"/>
@@ -1286,18 +1283,14 @@
     <col min="7" max="7" width="10.59765625" customWidth="1"/>
     <col min="8" max="8" width="16.46484375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.59765625" customWidth="1"/>
+    <col min="10" max="10" width="25.06640625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.59765625" customWidth="1"/>
     <col min="13" max="13" width="16.46484375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="25.06640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.59765625" customWidth="1"/>
-    <col min="18" max="18" width="16.46484375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="27" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="30.59765625" customWidth="1"/>
+    <col min="15" max="15" width="30.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>210</v>
       </c>
@@ -1309,12 +1302,12 @@
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -1322,7 +1315,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>59</v>
       </c>
@@ -1330,7 +1323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B9" s="5" t="s">
         <v>85</v>
       </c>
@@ -1340,11 +1333,8 @@
       <c r="L9" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="Q9" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.6">
       <c r="B10" s="6" t="s">
         <v>33</v>
       </c>
@@ -1381,20 +1371,8 @@
       <c r="O10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="Q10" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="R10" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="S10" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="T10" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B11" s="7" t="s">
         <v>88</v>
       </c>
@@ -1411,40 +1389,28 @@
         <v>88</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>211</v>
+        <v>89</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>212</v>
+        <v>90</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L11" s="7" t="s">
         <v>88</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>89</v>
+        <v>236</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>90</v>
+        <v>237</v>
       </c>
       <c r="O11" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="R11" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="S11" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="T11" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B12" s="8" t="s">
         <v>88</v>
       </c>
@@ -1461,40 +1427,28 @@
         <v>88</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>214</v>
+        <v>92</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>215</v>
+        <v>93</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>88</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>92</v>
+        <v>239</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>93</v>
+        <v>240</v>
       </c>
       <c r="O12" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q12" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="R12" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="S12" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="T12" s="8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B13" s="7" t="s">
         <v>88</v>
       </c>
@@ -1511,40 +1465,28 @@
         <v>88</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>216</v>
+        <v>94</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>217</v>
+        <v>95</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L13" s="7" t="s">
         <v>88</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="O13" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q13" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="S13" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="T13" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B14" s="8" t="s">
         <v>88</v>
       </c>
@@ -1561,40 +1503,28 @@
         <v>88</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>218</v>
+        <v>96</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>219</v>
+        <v>97</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L14" s="8" t="s">
         <v>88</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="S14" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="T14" s="8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B15" s="7" t="s">
         <v>88</v>
       </c>
@@ -1611,40 +1541,28 @@
         <v>88</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>220</v>
+        <v>98</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>221</v>
+        <v>99</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>88</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>98</v>
+        <v>241</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>99</v>
+        <v>242</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q15" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="S15" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="T15" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="B16" s="8" t="s">
         <v>88</v>
       </c>
@@ -1661,40 +1579,28 @@
         <v>88</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>222</v>
+        <v>100</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>223</v>
+        <v>101</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L16" s="8" t="s">
         <v>88</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>100</v>
+        <v>243</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>101</v>
+        <v>244</v>
       </c>
       <c r="O16" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q16" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="S16" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="T16" s="8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B17" s="7" t="s">
         <v>88</v>
       </c>
@@ -1711,40 +1617,28 @@
         <v>88</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>178</v>
+        <v>102</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>179</v>
+        <v>103</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L17" s="7" t="s">
         <v>88</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="O17" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="R17" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="S17" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="T17" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B18" s="8" t="s">
         <v>88</v>
       </c>
@@ -1761,40 +1655,28 @@
         <v>88</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>192</v>
+        <v>104</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>193</v>
+        <v>105</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>88</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>104</v>
+        <v>245</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>105</v>
+        <v>246</v>
       </c>
       <c r="O18" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q18" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="R18" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="S18" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="T18" s="8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B19" s="7" t="s">
         <v>88</v>
       </c>
@@ -1811,40 +1693,28 @@
         <v>88</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>224</v>
+        <v>106</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>225</v>
+        <v>107</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L19" s="7" t="s">
         <v>88</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>106</v>
+        <v>247</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>107</v>
+        <v>248</v>
       </c>
       <c r="O19" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q19" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="R19" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="S19" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="T19" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B20" s="8" t="s">
         <v>88</v>
       </c>
@@ -1861,40 +1731,28 @@
         <v>88</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>226</v>
+        <v>108</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>227</v>
+        <v>109</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>88</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>108</v>
+        <v>249</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>109</v>
+        <v>250</v>
       </c>
       <c r="O20" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q20" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="R20" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="S20" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="T20" s="8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B21" s="7" t="s">
         <v>88</v>
       </c>
@@ -1907,32 +1765,32 @@
       <c r="E21" s="7" t="s">
         <v>91</v>
       </c>
+      <c r="G21" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>211</v>
+      </c>
       <c r="L21" s="7" t="s">
         <v>88</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>110</v>
+        <v>251</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>111</v>
+        <v>252</v>
       </c>
       <c r="O21" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q21" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="R21" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="S21" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="T21" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B22" s="8" t="s">
         <v>88</v>
       </c>
@@ -1945,32 +1803,32 @@
       <c r="E22" s="8" t="s">
         <v>91</v>
       </c>
+      <c r="G22" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>211</v>
+      </c>
       <c r="L22" s="8" t="s">
         <v>88</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="N22" s="8" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="O22" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q22" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="R22" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="S22" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="T22" s="8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B23" s="7" t="s">
         <v>88</v>
       </c>
@@ -1983,32 +1841,32 @@
       <c r="E23" s="7" t="s">
         <v>91</v>
       </c>
+      <c r="G23" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>211</v>
+      </c>
       <c r="L23" s="7" t="s">
         <v>88</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>114</v>
+        <v>253</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>115</v>
+        <v>254</v>
       </c>
       <c r="O23" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="R23" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="S23" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="T23" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B24" s="8" t="s">
         <v>88</v>
       </c>
@@ -2021,32 +1879,32 @@
       <c r="E24" s="8" t="s">
         <v>91</v>
       </c>
+      <c r="G24" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>211</v>
+      </c>
       <c r="L24" s="8" t="s">
         <v>88</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>117</v>
+        <v>167</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q24" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="R24" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="S24" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="T24" s="8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B25" s="7" t="s">
         <v>88</v>
       </c>
@@ -2059,32 +1917,32 @@
       <c r="E25" s="7" t="s">
         <v>91</v>
       </c>
+      <c r="G25" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>211</v>
+      </c>
       <c r="L25" s="7" t="s">
         <v>88</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>118</v>
+        <v>255</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>119</v>
+        <v>256</v>
       </c>
       <c r="O25" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q25" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="R25" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="S25" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="T25" s="7" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B26" s="8" t="s">
         <v>88</v>
       </c>
@@ -2097,32 +1955,32 @@
       <c r="E26" s="8" t="s">
         <v>91</v>
       </c>
+      <c r="G26" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>211</v>
+      </c>
       <c r="L26" s="8" t="s">
         <v>88</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>120</v>
+        <v>224</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>121</v>
+        <v>225</v>
       </c>
       <c r="O26" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="Q26" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="R26" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="S26" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="T26" s="8" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.45">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B27" s="7" t="s">
         <v>88</v>
       </c>
@@ -2135,20 +1993,20 @@
       <c r="E27" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L27" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M27" s="7" t="s">
+      <c r="G27" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H27" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="N27" s="7" t="s">
+      <c r="I27" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="O27" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="J27" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B28" s="8" t="s">
         <v>88</v>
       </c>
@@ -2161,20 +2019,20 @@
       <c r="E28" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L28" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M28" s="8" t="s">
+      <c r="G28" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H28" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="N28" s="8" t="s">
+      <c r="I28" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="O28" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="J28" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B29" s="7" t="s">
         <v>88</v>
       </c>
@@ -2187,20 +2045,20 @@
       <c r="E29" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L29" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M29" s="7" t="s">
+      <c r="G29" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H29" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="N29" s="7" t="s">
+      <c r="I29" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="O29" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="J29" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B30" s="8" t="s">
         <v>88</v>
       </c>
@@ -2213,20 +2071,20 @@
       <c r="E30" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L30" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M30" s="8" t="s">
+      <c r="G30" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="N30" s="8" t="s">
+      <c r="I30" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="O30" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="J30" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B31" s="7" t="s">
         <v>88</v>
       </c>
@@ -2239,20 +2097,20 @@
       <c r="E31" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L31" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M31" s="7" t="s">
+      <c r="G31" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H31" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="N31" s="7" t="s">
+      <c r="I31" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="O31" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="J31" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B32" s="8" t="s">
         <v>88</v>
       </c>
@@ -2265,20 +2123,20 @@
       <c r="E32" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L32" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M32" s="8" t="s">
+      <c r="G32" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H32" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="N32" s="8" t="s">
+      <c r="I32" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="O32" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J32" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B33" s="7" t="s">
         <v>88</v>
       </c>
@@ -2291,20 +2149,20 @@
       <c r="E33" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L33" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M33" s="7" t="s">
+      <c r="G33" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H33" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="N33" s="7" t="s">
+      <c r="I33" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="O33" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J33" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B34" s="8" t="s">
         <v>88</v>
       </c>
@@ -2317,20 +2175,20 @@
       <c r="E34" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L34" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M34" s="8" t="s">
+      <c r="G34" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H34" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="N34" s="8" t="s">
+      <c r="I34" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="O34" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J34" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B35" s="7" t="s">
         <v>88</v>
       </c>
@@ -2343,20 +2201,20 @@
       <c r="E35" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L35" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M35" s="7" t="s">
+      <c r="G35" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H35" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="N35" s="7" t="s">
+      <c r="I35" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="O35" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J35" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B36" s="8" t="s">
         <v>88</v>
       </c>
@@ -2369,20 +2227,20 @@
       <c r="E36" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L36" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M36" s="8" t="s">
+      <c r="G36" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H36" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="N36" s="8" t="s">
+      <c r="I36" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="O36" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J36" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B37" s="7" t="s">
         <v>88</v>
       </c>
@@ -2395,20 +2253,20 @@
       <c r="E37" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L37" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M37" s="7" t="s">
+      <c r="G37" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H37" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="N37" s="7" t="s">
+      <c r="I37" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="O37" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J37" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B38" s="8" t="s">
         <v>88</v>
       </c>
@@ -2421,20 +2279,20 @@
       <c r="E38" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L38" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M38" s="8" t="s">
+      <c r="G38" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H38" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="N38" s="8" t="s">
+      <c r="I38" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="O38" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J38" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B39" s="7" t="s">
         <v>88</v>
       </c>
@@ -2447,20 +2305,20 @@
       <c r="E39" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L39" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M39" s="7" t="s">
+      <c r="G39" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H39" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="N39" s="7" t="s">
+      <c r="I39" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="O39" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J39" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B40" s="8" t="s">
         <v>88</v>
       </c>
@@ -2473,20 +2331,20 @@
       <c r="E40" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L40" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M40" s="8" t="s">
+      <c r="G40" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H40" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="N40" s="8" t="s">
+      <c r="I40" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="O40" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J40" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B41" s="7" t="s">
         <v>88</v>
       </c>
@@ -2499,20 +2357,20 @@
       <c r="E41" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L41" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M41" s="7" t="s">
+      <c r="G41" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H41" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="N41" s="7" t="s">
+      <c r="I41" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="O41" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J41" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B42" s="8" t="s">
         <v>88</v>
       </c>
@@ -2525,20 +2383,20 @@
       <c r="E42" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L42" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M42" s="8" t="s">
+      <c r="G42" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H42" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="N42" s="8" t="s">
+      <c r="I42" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="O42" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J42" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B43" s="7" t="s">
         <v>88</v>
       </c>
@@ -2551,20 +2409,20 @@
       <c r="E43" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L43" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M43" s="7" t="s">
+      <c r="G43" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H43" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="N43" s="7" t="s">
+      <c r="I43" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="O43" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J43" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B44" s="8" t="s">
         <v>88</v>
       </c>
@@ -2577,20 +2435,20 @@
       <c r="E44" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L44" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M44" s="8" t="s">
+      <c r="G44" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H44" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="N44" s="8" t="s">
+      <c r="I44" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="O44" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J44" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B45" s="7" t="s">
         <v>88</v>
       </c>
@@ -2603,20 +2461,20 @@
       <c r="E45" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L45" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M45" s="7" t="s">
+      <c r="G45" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H45" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="N45" s="7" t="s">
+      <c r="I45" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="O45" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J45" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B46" s="8" t="s">
         <v>88</v>
       </c>
@@ -2629,20 +2487,20 @@
       <c r="E46" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L46" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M46" s="8" t="s">
+      <c r="G46" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H46" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="N46" s="8" t="s">
+      <c r="I46" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="O46" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J46" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B47" s="7" t="s">
         <v>88</v>
       </c>
@@ -2655,20 +2513,20 @@
       <c r="E47" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L47" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M47" s="7" t="s">
+      <c r="G47" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H47" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="N47" s="7" t="s">
+      <c r="I47" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="O47" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J47" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B48" s="8" t="s">
         <v>88</v>
       </c>
@@ -2681,20 +2539,20 @@
       <c r="E48" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L48" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M48" s="8" t="s">
+      <c r="G48" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H48" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="N48" s="8" t="s">
+      <c r="I48" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="O48" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="49" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J48" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B49" s="7" t="s">
         <v>88</v>
       </c>
@@ -2707,20 +2565,20 @@
       <c r="E49" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L49" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M49" s="7" t="s">
+      <c r="G49" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H49" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="N49" s="7" t="s">
+      <c r="I49" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="O49" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="50" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J49" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B50" s="8" t="s">
         <v>88</v>
       </c>
@@ -2733,20 +2591,20 @@
       <c r="E50" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L50" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M50" s="8" t="s">
+      <c r="G50" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H50" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="N50" s="8" t="s">
+      <c r="I50" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="O50" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="51" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J50" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B51" s="7" t="s">
         <v>88</v>
       </c>
@@ -2759,20 +2617,20 @@
       <c r="E51" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L51" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M51" s="7" t="s">
+      <c r="G51" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H51" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="N51" s="7" t="s">
+      <c r="I51" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="O51" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="52" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J51" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B52" s="8" t="s">
         <v>88</v>
       </c>
@@ -2785,20 +2643,20 @@
       <c r="E52" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L52" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M52" s="8" t="s">
+      <c r="G52" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H52" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="N52" s="8" t="s">
+      <c r="I52" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="O52" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="53" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J52" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B53" s="7" t="s">
         <v>88</v>
       </c>
@@ -2811,20 +2669,20 @@
       <c r="E53" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L53" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M53" s="7" t="s">
+      <c r="G53" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H53" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="N53" s="7" t="s">
+      <c r="I53" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="O53" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="54" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J53" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B54" s="8" t="s">
         <v>88</v>
       </c>
@@ -2837,20 +2695,20 @@
       <c r="E54" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L54" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M54" s="8" t="s">
+      <c r="G54" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H54" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="N54" s="8" t="s">
+      <c r="I54" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="O54" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="55" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J54" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B55" s="7" t="s">
         <v>88</v>
       </c>
@@ -2863,20 +2721,20 @@
       <c r="E55" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L55" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M55" s="7" t="s">
+      <c r="G55" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H55" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="N55" s="7" t="s">
+      <c r="I55" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="O55" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="56" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J55" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B56" s="8" t="s">
         <v>88</v>
       </c>
@@ -2889,20 +2747,20 @@
       <c r="E56" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L56" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M56" s="8" t="s">
+      <c r="G56" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H56" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="N56" s="8" t="s">
+      <c r="I56" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="O56" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="57" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J56" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B57" s="7" t="s">
         <v>88</v>
       </c>
@@ -2915,20 +2773,20 @@
       <c r="E57" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L57" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M57" s="7" t="s">
+      <c r="G57" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H57" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="N57" s="7" t="s">
+      <c r="I57" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="O57" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="58" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J57" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B58" s="8" t="s">
         <v>88</v>
       </c>
@@ -2941,20 +2799,20 @@
       <c r="E58" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L58" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M58" s="8" t="s">
+      <c r="G58" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H58" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="N58" s="8" t="s">
+      <c r="I58" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="O58" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="59" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J58" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B59" s="7" t="s">
         <v>88</v>
       </c>
@@ -2967,20 +2825,20 @@
       <c r="E59" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L59" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M59" s="7" t="s">
+      <c r="G59" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H59" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="N59" s="7" t="s">
+      <c r="I59" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="O59" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="60" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J59" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B60" s="8" t="s">
         <v>88</v>
       </c>
@@ -2993,20 +2851,20 @@
       <c r="E60" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L60" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M60" s="8" t="s">
+      <c r="G60" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H60" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="N60" s="8" t="s">
+      <c r="I60" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="O60" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="61" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J60" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B61" s="7" t="s">
         <v>88</v>
       </c>
@@ -3019,20 +2877,20 @@
       <c r="E61" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L61" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M61" s="7" t="s">
+      <c r="G61" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H61" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="N61" s="7" t="s">
+      <c r="I61" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="O61" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="62" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J61" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B62" s="8" t="s">
         <v>88</v>
       </c>
@@ -3045,20 +2903,20 @@
       <c r="E62" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L62" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M62" s="8" t="s">
+      <c r="G62" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H62" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="N62" s="8" t="s">
+      <c r="I62" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="O62" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="63" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J62" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B63" s="7" t="s">
         <v>88</v>
       </c>
@@ -3071,20 +2929,20 @@
       <c r="E63" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L63" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M63" s="7" t="s">
+      <c r="G63" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H63" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="N63" s="7" t="s">
+      <c r="I63" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="O63" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="64" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J63" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B64" s="8" t="s">
         <v>88</v>
       </c>
@@ -3097,20 +2955,20 @@
       <c r="E64" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L64" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M64" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="N64" s="8" t="s">
+      <c r="G64" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H64" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="O64" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="I64" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="J64" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B65" s="7" t="s">
         <v>88</v>
       </c>
@@ -3123,20 +2981,20 @@
       <c r="E65" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L65" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M65" s="7" t="s">
+      <c r="G65" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H65" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="N65" s="7" t="s">
+      <c r="I65" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="O65" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J65" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B66" s="8" t="s">
         <v>88</v>
       </c>
@@ -3149,20 +3007,20 @@
       <c r="E66" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L66" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M66" s="8" t="s">
+      <c r="G66" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H66" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="N66" s="8" t="s">
+      <c r="I66" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="O66" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J66" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B67" s="7" t="s">
         <v>88</v>
       </c>
@@ -3175,20 +3033,20 @@
       <c r="E67" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L67" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M67" s="7" t="s">
+      <c r="G67" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H67" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="N67" s="7" t="s">
+      <c r="I67" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="O67" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J67" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B68" s="8" t="s">
         <v>88</v>
       </c>
@@ -3201,20 +3059,20 @@
       <c r="E68" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L68" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M68" s="8" t="s">
+      <c r="G68" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H68" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="N68" s="8" t="s">
+      <c r="I68" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="O68" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J68" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B69" s="7" t="s">
         <v>88</v>
       </c>
@@ -3227,20 +3085,20 @@
       <c r="E69" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="L69" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M69" s="7" t="s">
+      <c r="G69" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H69" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="N69" s="7" t="s">
+      <c r="I69" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="O69" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="J69" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B70" s="8" t="s">
         <v>88</v>
       </c>
@@ -3253,185 +3111,185 @@
       <c r="E70" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="L70" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M70" s="8" t="s">
+      <c r="G70" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H70" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="N70" s="8" t="s">
+      <c r="I70" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="O70" s="8" t="s">
+      <c r="J70" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G71" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="I71" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="J71" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G72" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H72" s="8" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L71" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M71" s="7" t="s">
+      <c r="I72" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="N71" s="7" t="s">
+      <c r="J72" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G73" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H73" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="O71" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L72" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M72" s="8" t="s">
+      <c r="I73" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="N72" s="8" t="s">
+      <c r="J73" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G74" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="J74" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G75" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H75" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="O72" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L73" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M73" s="7" t="s">
+      <c r="I75" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="N73" s="7" t="s">
+      <c r="J75" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G76" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H76" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="I76" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="J76" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G77" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="I77" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G78" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H78" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="J78" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G79" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G80" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H80" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="O73" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L74" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M74" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="N74" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="O74" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L75" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M75" s="7" t="s">
+      <c r="I80" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="N75" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="O75" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L76" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M76" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="N76" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="O76" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L77" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M77" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="N77" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="O77" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="78" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L78" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M78" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="N78" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="O78" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L79" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M79" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="N79" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="O79" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="L80" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M80" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="N80" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="O80" s="8" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="81" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L81" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M81" s="7" t="s">
+      <c r="J80" s="8" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="81" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G81" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H81" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="N81" s="7" t="s">
+      <c r="I81" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="O81" s="7" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="82" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L82" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M82" s="8" t="s">
+      <c r="J81" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="82" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G82" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="H82" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="N82" s="8" t="s">
+      <c r="I82" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="O82" s="8" t="s">
-        <v>228</v>
+      <c r="J82" s="8" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{885E1FFF-B243-4D54-B3DA-6B5004A54BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{364928E4-25E4-4C73-A671-28583CDCDF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="256">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -668,9 +668,6 @@
   </si>
   <si>
     <t>at grid node - w255284259-400_POL</t>
-  </si>
-  <si>
-    <t>VERVESTACKS - the open USE platform · Powered by data · Shaped by vision · Guided by intuition · Fueled by passion</t>
   </si>
   <si>
     <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
@@ -815,7 +812,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -830,61 +827,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="7"/>
-      <color rgb="FF969696"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF19375F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4F81BD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7F9FC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -892,52 +844,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -953,61 +868,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>63500</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1054100</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>266700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD170467-8275-13C1-A7A8-239E979325B4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5245100" y="12700"/>
-          <a:ext cx="990600" cy="254000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1273,41 +1133,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="A1:O82"/>
+  <dimension ref="B3:O82"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="2" max="2" width="10.59765625" customWidth="1"/>
-    <col min="3" max="3" width="16.46484375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.59765625" customWidth="1"/>
-    <col min="7" max="7" width="10.59765625" customWidth="1"/>
-    <col min="8" max="8" width="16.46484375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.06640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.59765625" customWidth="1"/>
-    <col min="13" max="13" width="16.46484375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="30.59765625" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="22.05" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -1315,7 +1149,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>59</v>
       </c>
@@ -1323,1981 +1157,1977 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="B9" s="5" t="s">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" t="s">
         <v>85</v>
       </c>
-      <c r="L9" s="5" t="s">
+      <c r="L9" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="B10" s="6" t="s">
+    <row r="10" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" t="s">
         <v>86</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" t="s">
         <v>87</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" t="s">
         <v>21</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" t="s">
         <v>33</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" t="s">
         <v>86</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="N10" t="s">
         <v>87</v>
       </c>
-      <c r="O10" s="6" t="s">
+      <c r="O10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B11" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="7" t="s">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
         <v>89</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" t="s">
         <v>90</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H11" s="7" t="s">
+      <c r="E11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G11" t="s">
+        <v>88</v>
+      </c>
+      <c r="H11" t="s">
         <v>89</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" t="s">
         <v>90</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" t="s">
+        <v>210</v>
+      </c>
+      <c r="L11" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" t="s">
+        <v>235</v>
+      </c>
+      <c r="N11" t="s">
+        <v>236</v>
+      </c>
+      <c r="O11" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" t="s">
+        <v>92</v>
+      </c>
+      <c r="I12" t="s">
+        <v>93</v>
+      </c>
+      <c r="J12" t="s">
+        <v>210</v>
+      </c>
+      <c r="L12" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" t="s">
+        <v>238</v>
+      </c>
+      <c r="N12" t="s">
+        <v>239</v>
+      </c>
+      <c r="O12" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13" t="s">
+        <v>95</v>
+      </c>
+      <c r="J13" t="s">
+        <v>210</v>
+      </c>
+      <c r="L13" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" t="s">
+        <v>106</v>
+      </c>
+      <c r="N13" t="s">
+        <v>107</v>
+      </c>
+      <c r="O13" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H14" t="s">
+        <v>96</v>
+      </c>
+      <c r="I14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J14" t="s">
+        <v>210</v>
+      </c>
+      <c r="L14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" t="s">
+        <v>128</v>
+      </c>
+      <c r="N14" t="s">
+        <v>129</v>
+      </c>
+      <c r="O14" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" t="s">
+        <v>98</v>
+      </c>
+      <c r="I15" t="s">
+        <v>99</v>
+      </c>
+      <c r="J15" t="s">
+        <v>210</v>
+      </c>
+      <c r="L15" t="s">
+        <v>88</v>
+      </c>
+      <c r="M15" t="s">
+        <v>240</v>
+      </c>
+      <c r="N15" t="s">
+        <v>241</v>
+      </c>
+      <c r="O15" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" t="s">
+        <v>91</v>
+      </c>
+      <c r="G16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H16" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" t="s">
+        <v>101</v>
+      </c>
+      <c r="J16" t="s">
+        <v>210</v>
+      </c>
+      <c r="L16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M16" t="s">
+        <v>242</v>
+      </c>
+      <c r="N16" t="s">
+        <v>243</v>
+      </c>
+      <c r="O16" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" t="s">
+        <v>102</v>
+      </c>
+      <c r="D17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G17" t="s">
+        <v>88</v>
+      </c>
+      <c r="H17" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" t="s">
+        <v>210</v>
+      </c>
+      <c r="L17" t="s">
+        <v>88</v>
+      </c>
+      <c r="M17" t="s">
+        <v>140</v>
+      </c>
+      <c r="N17" t="s">
+        <v>141</v>
+      </c>
+      <c r="O17" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H18" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" t="s">
+        <v>105</v>
+      </c>
+      <c r="J18" t="s">
+        <v>210</v>
+      </c>
+      <c r="L18" t="s">
+        <v>88</v>
+      </c>
+      <c r="M18" t="s">
+        <v>244</v>
+      </c>
+      <c r="N18" t="s">
+        <v>245</v>
+      </c>
+      <c r="O18" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" t="s">
+        <v>107</v>
+      </c>
+      <c r="J19" t="s">
+        <v>210</v>
+      </c>
+      <c r="L19" t="s">
+        <v>88</v>
+      </c>
+      <c r="M19" t="s">
+        <v>246</v>
+      </c>
+      <c r="N19" t="s">
+        <v>247</v>
+      </c>
+      <c r="O19" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" t="s">
+        <v>108</v>
+      </c>
+      <c r="I20" t="s">
+        <v>109</v>
+      </c>
+      <c r="J20" t="s">
+        <v>210</v>
+      </c>
+      <c r="L20" t="s">
+        <v>88</v>
+      </c>
+      <c r="M20" t="s">
+        <v>248</v>
+      </c>
+      <c r="N20" t="s">
+        <v>249</v>
+      </c>
+      <c r="O20" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" t="s">
+        <v>91</v>
+      </c>
+      <c r="G21" t="s">
+        <v>88</v>
+      </c>
+      <c r="H21" t="s">
+        <v>110</v>
+      </c>
+      <c r="I21" t="s">
+        <v>111</v>
+      </c>
+      <c r="J21" t="s">
+        <v>210</v>
+      </c>
+      <c r="L21" t="s">
+        <v>88</v>
+      </c>
+      <c r="M21" t="s">
+        <v>250</v>
+      </c>
+      <c r="N21" t="s">
+        <v>251</v>
+      </c>
+      <c r="O21" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>112</v>
+      </c>
+      <c r="D22" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" t="s">
+        <v>88</v>
+      </c>
+      <c r="H22" t="s">
+        <v>112</v>
+      </c>
+      <c r="I22" t="s">
+        <v>113</v>
+      </c>
+      <c r="J22" t="s">
+        <v>210</v>
+      </c>
+      <c r="L22" t="s">
+        <v>88</v>
+      </c>
+      <c r="M22" t="s">
+        <v>94</v>
+      </c>
+      <c r="N22" t="s">
+        <v>95</v>
+      </c>
+      <c r="O22" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>114</v>
+      </c>
+      <c r="D23" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" t="s">
+        <v>88</v>
+      </c>
+      <c r="H23" t="s">
+        <v>114</v>
+      </c>
+      <c r="I23" t="s">
+        <v>115</v>
+      </c>
+      <c r="J23" t="s">
+        <v>210</v>
+      </c>
+      <c r="L23" t="s">
+        <v>88</v>
+      </c>
+      <c r="M23" t="s">
+        <v>252</v>
+      </c>
+      <c r="N23" t="s">
+        <v>253</v>
+      </c>
+      <c r="O23" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" t="s">
+        <v>91</v>
+      </c>
+      <c r="G24" t="s">
+        <v>88</v>
+      </c>
+      <c r="H24" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" t="s">
+        <v>117</v>
+      </c>
+      <c r="J24" t="s">
+        <v>210</v>
+      </c>
+      <c r="L24" t="s">
+        <v>88</v>
+      </c>
+      <c r="M24" t="s">
+        <v>166</v>
+      </c>
+      <c r="N24" t="s">
+        <v>167</v>
+      </c>
+      <c r="O24" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" t="s">
+        <v>91</v>
+      </c>
+      <c r="G25" t="s">
+        <v>88</v>
+      </c>
+      <c r="H25" t="s">
+        <v>118</v>
+      </c>
+      <c r="I25" t="s">
+        <v>119</v>
+      </c>
+      <c r="J25" t="s">
+        <v>210</v>
+      </c>
+      <c r="L25" t="s">
+        <v>88</v>
+      </c>
+      <c r="M25" t="s">
+        <v>254</v>
+      </c>
+      <c r="N25" t="s">
+        <v>255</v>
+      </c>
+      <c r="O25" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" t="s">
+        <v>121</v>
+      </c>
+      <c r="E26" t="s">
+        <v>91</v>
+      </c>
+      <c r="G26" t="s">
+        <v>88</v>
+      </c>
+      <c r="H26" t="s">
+        <v>120</v>
+      </c>
+      <c r="I26" t="s">
+        <v>121</v>
+      </c>
+      <c r="J26" t="s">
+        <v>210</v>
+      </c>
+      <c r="L26" t="s">
+        <v>88</v>
+      </c>
+      <c r="M26" t="s">
+        <v>223</v>
+      </c>
+      <c r="N26" t="s">
+        <v>224</v>
+      </c>
+      <c r="O26" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" t="s">
+        <v>123</v>
+      </c>
+      <c r="E27" t="s">
+        <v>91</v>
+      </c>
+      <c r="G27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H27" t="s">
+        <v>122</v>
+      </c>
+      <c r="I27" t="s">
+        <v>123</v>
+      </c>
+      <c r="J27" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" t="s">
+        <v>125</v>
+      </c>
+      <c r="E28" t="s">
+        <v>91</v>
+      </c>
+      <c r="G28" t="s">
+        <v>88</v>
+      </c>
+      <c r="H28" t="s">
+        <v>124</v>
+      </c>
+      <c r="I28" t="s">
+        <v>125</v>
+      </c>
+      <c r="J28" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29" t="s">
+        <v>88</v>
+      </c>
+      <c r="H29" t="s">
+        <v>126</v>
+      </c>
+      <c r="I29" t="s">
+        <v>127</v>
+      </c>
+      <c r="J29" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" t="s">
+        <v>128</v>
+      </c>
+      <c r="D30" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" t="s">
+        <v>91</v>
+      </c>
+      <c r="G30" t="s">
+        <v>88</v>
+      </c>
+      <c r="H30" t="s">
+        <v>128</v>
+      </c>
+      <c r="I30" t="s">
+        <v>129</v>
+      </c>
+      <c r="J30" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" t="s">
+        <v>130</v>
+      </c>
+      <c r="D31" t="s">
+        <v>131</v>
+      </c>
+      <c r="E31" t="s">
+        <v>91</v>
+      </c>
+      <c r="G31" t="s">
+        <v>88</v>
+      </c>
+      <c r="H31" t="s">
+        <v>130</v>
+      </c>
+      <c r="I31" t="s">
+        <v>131</v>
+      </c>
+      <c r="J31" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" t="s">
+        <v>132</v>
+      </c>
+      <c r="D32" t="s">
+        <v>133</v>
+      </c>
+      <c r="E32" t="s">
+        <v>91</v>
+      </c>
+      <c r="G32" t="s">
+        <v>88</v>
+      </c>
+      <c r="H32" t="s">
+        <v>132</v>
+      </c>
+      <c r="I32" t="s">
+        <v>133</v>
+      </c>
+      <c r="J32" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" t="s">
+        <v>134</v>
+      </c>
+      <c r="D33" t="s">
+        <v>135</v>
+      </c>
+      <c r="E33" t="s">
+        <v>91</v>
+      </c>
+      <c r="G33" t="s">
+        <v>88</v>
+      </c>
+      <c r="H33" t="s">
+        <v>134</v>
+      </c>
+      <c r="I33" t="s">
+        <v>135</v>
+      </c>
+      <c r="J33" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" t="s">
+        <v>136</v>
+      </c>
+      <c r="D34" t="s">
+        <v>137</v>
+      </c>
+      <c r="E34" t="s">
+        <v>91</v>
+      </c>
+      <c r="G34" t="s">
+        <v>88</v>
+      </c>
+      <c r="H34" t="s">
+        <v>136</v>
+      </c>
+      <c r="I34" t="s">
+        <v>137</v>
+      </c>
+      <c r="J34" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B35" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" t="s">
+        <v>91</v>
+      </c>
+      <c r="G35" t="s">
+        <v>88</v>
+      </c>
+      <c r="H35" t="s">
+        <v>138</v>
+      </c>
+      <c r="I35" t="s">
+        <v>139</v>
+      </c>
+      <c r="J35" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B36" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" t="s">
+        <v>140</v>
+      </c>
+      <c r="D36" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" t="s">
+        <v>91</v>
+      </c>
+      <c r="G36" t="s">
+        <v>88</v>
+      </c>
+      <c r="H36" t="s">
+        <v>140</v>
+      </c>
+      <c r="I36" t="s">
+        <v>141</v>
+      </c>
+      <c r="J36" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B37" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" t="s">
+        <v>142</v>
+      </c>
+      <c r="D37" t="s">
+        <v>143</v>
+      </c>
+      <c r="E37" t="s">
+        <v>91</v>
+      </c>
+      <c r="G37" t="s">
+        <v>88</v>
+      </c>
+      <c r="H37" t="s">
+        <v>142</v>
+      </c>
+      <c r="I37" t="s">
+        <v>143</v>
+      </c>
+      <c r="J37" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38" t="s">
+        <v>145</v>
+      </c>
+      <c r="E38" t="s">
+        <v>91</v>
+      </c>
+      <c r="G38" t="s">
+        <v>88</v>
+      </c>
+      <c r="H38" t="s">
+        <v>144</v>
+      </c>
+      <c r="I38" t="s">
+        <v>145</v>
+      </c>
+      <c r="J38" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" t="s">
+        <v>91</v>
+      </c>
+      <c r="G39" t="s">
+        <v>88</v>
+      </c>
+      <c r="H39" t="s">
+        <v>146</v>
+      </c>
+      <c r="I39" t="s">
+        <v>147</v>
+      </c>
+      <c r="J39" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B40" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" t="s">
+        <v>148</v>
+      </c>
+      <c r="D40" t="s">
+        <v>149</v>
+      </c>
+      <c r="E40" t="s">
+        <v>91</v>
+      </c>
+      <c r="G40" t="s">
+        <v>88</v>
+      </c>
+      <c r="H40" t="s">
+        <v>148</v>
+      </c>
+      <c r="I40" t="s">
+        <v>149</v>
+      </c>
+      <c r="J40" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" t="s">
+        <v>150</v>
+      </c>
+      <c r="D41" t="s">
+        <v>151</v>
+      </c>
+      <c r="E41" t="s">
+        <v>91</v>
+      </c>
+      <c r="G41" t="s">
+        <v>88</v>
+      </c>
+      <c r="H41" t="s">
+        <v>150</v>
+      </c>
+      <c r="I41" t="s">
+        <v>151</v>
+      </c>
+      <c r="J41" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" t="s">
+        <v>152</v>
+      </c>
+      <c r="D42" t="s">
+        <v>153</v>
+      </c>
+      <c r="E42" t="s">
+        <v>91</v>
+      </c>
+      <c r="G42" t="s">
+        <v>88</v>
+      </c>
+      <c r="H42" t="s">
+        <v>152</v>
+      </c>
+      <c r="I42" t="s">
+        <v>153</v>
+      </c>
+      <c r="J42" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" t="s">
+        <v>154</v>
+      </c>
+      <c r="D43" t="s">
+        <v>155</v>
+      </c>
+      <c r="E43" t="s">
+        <v>91</v>
+      </c>
+      <c r="G43" t="s">
+        <v>88</v>
+      </c>
+      <c r="H43" t="s">
+        <v>154</v>
+      </c>
+      <c r="I43" t="s">
+        <v>155</v>
+      </c>
+      <c r="J43" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B44" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" t="s">
+        <v>156</v>
+      </c>
+      <c r="D44" t="s">
+        <v>157</v>
+      </c>
+      <c r="E44" t="s">
+        <v>91</v>
+      </c>
+      <c r="G44" t="s">
+        <v>88</v>
+      </c>
+      <c r="H44" t="s">
+        <v>156</v>
+      </c>
+      <c r="I44" t="s">
+        <v>157</v>
+      </c>
+      <c r="J44" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B45" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" t="s">
+        <v>158</v>
+      </c>
+      <c r="D45" t="s">
+        <v>159</v>
+      </c>
+      <c r="E45" t="s">
+        <v>91</v>
+      </c>
+      <c r="G45" t="s">
+        <v>88</v>
+      </c>
+      <c r="H45" t="s">
+        <v>158</v>
+      </c>
+      <c r="I45" t="s">
+        <v>159</v>
+      </c>
+      <c r="J45" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" t="s">
+        <v>160</v>
+      </c>
+      <c r="D46" t="s">
+        <v>161</v>
+      </c>
+      <c r="E46" t="s">
+        <v>91</v>
+      </c>
+      <c r="G46" t="s">
+        <v>88</v>
+      </c>
+      <c r="H46" t="s">
+        <v>160</v>
+      </c>
+      <c r="I46" t="s">
+        <v>161</v>
+      </c>
+      <c r="J46" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" t="s">
+        <v>162</v>
+      </c>
+      <c r="D47" t="s">
+        <v>163</v>
+      </c>
+      <c r="E47" t="s">
+        <v>91</v>
+      </c>
+      <c r="G47" t="s">
+        <v>88</v>
+      </c>
+      <c r="H47" t="s">
+        <v>162</v>
+      </c>
+      <c r="I47" t="s">
+        <v>163</v>
+      </c>
+      <c r="J47" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B48" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" t="s">
+        <v>164</v>
+      </c>
+      <c r="D48" t="s">
+        <v>165</v>
+      </c>
+      <c r="E48" t="s">
+        <v>91</v>
+      </c>
+      <c r="G48" t="s">
+        <v>88</v>
+      </c>
+      <c r="H48" t="s">
+        <v>164</v>
+      </c>
+      <c r="I48" t="s">
+        <v>165</v>
+      </c>
+      <c r="J48" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B49" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" t="s">
+        <v>166</v>
+      </c>
+      <c r="D49" t="s">
+        <v>167</v>
+      </c>
+      <c r="E49" t="s">
+        <v>91</v>
+      </c>
+      <c r="G49" t="s">
+        <v>88</v>
+      </c>
+      <c r="H49" t="s">
+        <v>166</v>
+      </c>
+      <c r="I49" t="s">
+        <v>167</v>
+      </c>
+      <c r="J49" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B50" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" t="s">
+        <v>168</v>
+      </c>
+      <c r="D50" t="s">
+        <v>169</v>
+      </c>
+      <c r="E50" t="s">
+        <v>91</v>
+      </c>
+      <c r="G50" t="s">
+        <v>88</v>
+      </c>
+      <c r="H50" t="s">
+        <v>168</v>
+      </c>
+      <c r="I50" t="s">
+        <v>169</v>
+      </c>
+      <c r="J50" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" t="s">
+        <v>170</v>
+      </c>
+      <c r="D51" t="s">
+        <v>171</v>
+      </c>
+      <c r="E51" t="s">
+        <v>91</v>
+      </c>
+      <c r="G51" t="s">
+        <v>88</v>
+      </c>
+      <c r="H51" t="s">
+        <v>170</v>
+      </c>
+      <c r="I51" t="s">
+        <v>171</v>
+      </c>
+      <c r="J51" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B52" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" t="s">
+        <v>172</v>
+      </c>
+      <c r="D52" t="s">
+        <v>173</v>
+      </c>
+      <c r="E52" t="s">
+        <v>91</v>
+      </c>
+      <c r="G52" t="s">
+        <v>88</v>
+      </c>
+      <c r="H52" t="s">
+        <v>172</v>
+      </c>
+      <c r="I52" t="s">
+        <v>173</v>
+      </c>
+      <c r="J52" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B53" t="s">
+        <v>88</v>
+      </c>
+      <c r="C53" t="s">
+        <v>174</v>
+      </c>
+      <c r="D53" t="s">
+        <v>175</v>
+      </c>
+      <c r="E53" t="s">
+        <v>91</v>
+      </c>
+      <c r="G53" t="s">
+        <v>88</v>
+      </c>
+      <c r="H53" t="s">
+        <v>174</v>
+      </c>
+      <c r="I53" t="s">
+        <v>175</v>
+      </c>
+      <c r="J53" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B54" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" t="s">
+        <v>176</v>
+      </c>
+      <c r="D54" t="s">
+        <v>177</v>
+      </c>
+      <c r="E54" t="s">
+        <v>91</v>
+      </c>
+      <c r="G54" t="s">
+        <v>88</v>
+      </c>
+      <c r="H54" t="s">
+        <v>176</v>
+      </c>
+      <c r="I54" t="s">
+        <v>177</v>
+      </c>
+      <c r="J54" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B55" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" t="s">
+        <v>178</v>
+      </c>
+      <c r="D55" t="s">
+        <v>179</v>
+      </c>
+      <c r="E55" t="s">
+        <v>91</v>
+      </c>
+      <c r="G55" t="s">
+        <v>88</v>
+      </c>
+      <c r="H55" t="s">
+        <v>178</v>
+      </c>
+      <c r="I55" t="s">
+        <v>179</v>
+      </c>
+      <c r="J55" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B56" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" t="s">
+        <v>180</v>
+      </c>
+      <c r="D56" t="s">
+        <v>181</v>
+      </c>
+      <c r="E56" t="s">
+        <v>91</v>
+      </c>
+      <c r="G56" t="s">
+        <v>88</v>
+      </c>
+      <c r="H56" t="s">
+        <v>180</v>
+      </c>
+      <c r="I56" t="s">
+        <v>181</v>
+      </c>
+      <c r="J56" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B57" t="s">
+        <v>88</v>
+      </c>
+      <c r="C57" t="s">
+        <v>182</v>
+      </c>
+      <c r="D57" t="s">
+        <v>183</v>
+      </c>
+      <c r="E57" t="s">
+        <v>91</v>
+      </c>
+      <c r="G57" t="s">
+        <v>88</v>
+      </c>
+      <c r="H57" t="s">
+        <v>182</v>
+      </c>
+      <c r="I57" t="s">
+        <v>183</v>
+      </c>
+      <c r="J57" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B58" t="s">
+        <v>88</v>
+      </c>
+      <c r="C58" t="s">
+        <v>184</v>
+      </c>
+      <c r="D58" t="s">
+        <v>185</v>
+      </c>
+      <c r="E58" t="s">
+        <v>91</v>
+      </c>
+      <c r="G58" t="s">
+        <v>88</v>
+      </c>
+      <c r="H58" t="s">
+        <v>184</v>
+      </c>
+      <c r="I58" t="s">
+        <v>185</v>
+      </c>
+      <c r="J58" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B59" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59" t="s">
+        <v>186</v>
+      </c>
+      <c r="D59" t="s">
+        <v>187</v>
+      </c>
+      <c r="E59" t="s">
+        <v>91</v>
+      </c>
+      <c r="G59" t="s">
+        <v>88</v>
+      </c>
+      <c r="H59" t="s">
+        <v>186</v>
+      </c>
+      <c r="I59" t="s">
+        <v>187</v>
+      </c>
+      <c r="J59" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B60" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" t="s">
+        <v>188</v>
+      </c>
+      <c r="D60" t="s">
+        <v>189</v>
+      </c>
+      <c r="E60" t="s">
+        <v>91</v>
+      </c>
+      <c r="G60" t="s">
+        <v>88</v>
+      </c>
+      <c r="H60" t="s">
+        <v>188</v>
+      </c>
+      <c r="I60" t="s">
+        <v>189</v>
+      </c>
+      <c r="J60" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B61" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" t="s">
+        <v>190</v>
+      </c>
+      <c r="D61" t="s">
+        <v>191</v>
+      </c>
+      <c r="E61" t="s">
+        <v>91</v>
+      </c>
+      <c r="G61" t="s">
+        <v>88</v>
+      </c>
+      <c r="H61" t="s">
+        <v>190</v>
+      </c>
+      <c r="I61" t="s">
+        <v>191</v>
+      </c>
+      <c r="J61" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B62" t="s">
+        <v>88</v>
+      </c>
+      <c r="C62" t="s">
+        <v>192</v>
+      </c>
+      <c r="D62" t="s">
+        <v>193</v>
+      </c>
+      <c r="E62" t="s">
+        <v>91</v>
+      </c>
+      <c r="G62" t="s">
+        <v>88</v>
+      </c>
+      <c r="H62" t="s">
+        <v>192</v>
+      </c>
+      <c r="I62" t="s">
+        <v>193</v>
+      </c>
+      <c r="J62" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B63" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" t="s">
+        <v>194</v>
+      </c>
+      <c r="D63" t="s">
+        <v>195</v>
+      </c>
+      <c r="E63" t="s">
+        <v>91</v>
+      </c>
+      <c r="G63" t="s">
+        <v>88</v>
+      </c>
+      <c r="H63" t="s">
+        <v>194</v>
+      </c>
+      <c r="I63" t="s">
+        <v>195</v>
+      </c>
+      <c r="J63" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B64" t="s">
+        <v>88</v>
+      </c>
+      <c r="C64" t="s">
+        <v>196</v>
+      </c>
+      <c r="D64" t="s">
+        <v>197</v>
+      </c>
+      <c r="E64" t="s">
+        <v>91</v>
+      </c>
+      <c r="G64" t="s">
+        <v>88</v>
+      </c>
+      <c r="H64" t="s">
         <v>211</v>
       </c>
-      <c r="L11" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B12" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M12" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="N12" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="O12" s="8" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B13" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B15" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="B16" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M17" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="O17" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B18" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M18" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B19" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="O19" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B20" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M20" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="N20" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B21" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="O21" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B22" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="J22" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M22" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B23" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="N23" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="O23" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B24" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M24" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="N24" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="O24" s="8" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B25" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="O25" s="7" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B26" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G26" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="J26" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="M26" s="8" t="s">
+      <c r="I64" t="s">
+        <v>212</v>
+      </c>
+      <c r="J64" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B65" t="s">
+        <v>88</v>
+      </c>
+      <c r="C65" t="s">
+        <v>198</v>
+      </c>
+      <c r="D65" t="s">
+        <v>199</v>
+      </c>
+      <c r="E65" t="s">
+        <v>91</v>
+      </c>
+      <c r="G65" t="s">
+        <v>88</v>
+      </c>
+      <c r="H65" t="s">
+        <v>213</v>
+      </c>
+      <c r="I65" t="s">
+        <v>214</v>
+      </c>
+      <c r="J65" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B66" t="s">
+        <v>88</v>
+      </c>
+      <c r="C66" t="s">
+        <v>200</v>
+      </c>
+      <c r="D66" t="s">
+        <v>201</v>
+      </c>
+      <c r="E66" t="s">
+        <v>91</v>
+      </c>
+      <c r="G66" t="s">
+        <v>88</v>
+      </c>
+      <c r="H66" t="s">
+        <v>215</v>
+      </c>
+      <c r="I66" t="s">
+        <v>216</v>
+      </c>
+      <c r="J66" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B67" t="s">
+        <v>88</v>
+      </c>
+      <c r="C67" t="s">
+        <v>202</v>
+      </c>
+      <c r="D67" t="s">
+        <v>203</v>
+      </c>
+      <c r="E67" t="s">
+        <v>91</v>
+      </c>
+      <c r="G67" t="s">
+        <v>88</v>
+      </c>
+      <c r="H67" t="s">
+        <v>217</v>
+      </c>
+      <c r="I67" t="s">
+        <v>218</v>
+      </c>
+      <c r="J67" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B68" t="s">
+        <v>88</v>
+      </c>
+      <c r="C68" t="s">
+        <v>204</v>
+      </c>
+      <c r="D68" t="s">
+        <v>205</v>
+      </c>
+      <c r="E68" t="s">
+        <v>91</v>
+      </c>
+      <c r="G68" t="s">
+        <v>88</v>
+      </c>
+      <c r="H68" t="s">
+        <v>219</v>
+      </c>
+      <c r="I68" t="s">
+        <v>220</v>
+      </c>
+      <c r="J68" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B69" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" t="s">
+        <v>206</v>
+      </c>
+      <c r="D69" t="s">
+        <v>207</v>
+      </c>
+      <c r="E69" t="s">
+        <v>91</v>
+      </c>
+      <c r="G69" t="s">
+        <v>88</v>
+      </c>
+      <c r="H69" t="s">
+        <v>221</v>
+      </c>
+      <c r="I69" t="s">
+        <v>222</v>
+      </c>
+      <c r="J69" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B70" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" t="s">
+        <v>208</v>
+      </c>
+      <c r="D70" t="s">
+        <v>209</v>
+      </c>
+      <c r="E70" t="s">
+        <v>91</v>
+      </c>
+      <c r="G70" t="s">
+        <v>88</v>
+      </c>
+      <c r="H70" t="s">
+        <v>223</v>
+      </c>
+      <c r="I70" t="s">
         <v>224</v>
       </c>
-      <c r="N26" s="8" t="s">
+      <c r="J70" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G71" t="s">
+        <v>88</v>
+      </c>
+      <c r="H71" t="s">
         <v>225</v>
       </c>
-      <c r="O26" s="8" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B27" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B28" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G28" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="J28" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B29" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B30" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="J30" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B31" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.45">
-      <c r="B32" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G32" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="J32" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B33" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B34" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G34" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="I34" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="J34" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B35" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B36" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G36" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="I36" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="J36" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B37" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B38" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="I38" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J38" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B39" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B40" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="J40" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B41" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B42" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G42" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="I42" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="J42" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B43" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="J43" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B44" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="I44" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="J44" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B45" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B46" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="I46" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="J46" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B47" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="I47" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="J47" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B48" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="I48" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="J48" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B49" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H49" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="I49" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B50" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="I50" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="J50" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B51" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="I51" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B52" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H52" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="I52" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="J52" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B53" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="J53" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B54" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H54" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="I54" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="J54" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B55" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="J55" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B56" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="E56" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H56" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="I56" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="J56" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B57" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H57" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="I57" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J57" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B58" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C58" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H58" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="I58" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="J58" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B59" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="J59" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B60" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="I60" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="J60" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B61" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="I61" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="J61" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B62" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="D62" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H62" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="I62" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="J62" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B63" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="I63" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="J63" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B64" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C64" s="8" t="s">
+      <c r="I71" t="s">
+        <v>226</v>
+      </c>
+      <c r="J71" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G72" t="s">
+        <v>88</v>
+      </c>
+      <c r="H72" t="s">
+        <v>227</v>
+      </c>
+      <c r="I72" t="s">
+        <v>228</v>
+      </c>
+      <c r="J72" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G73" t="s">
+        <v>88</v>
+      </c>
+      <c r="H73" t="s">
+        <v>229</v>
+      </c>
+      <c r="I73" t="s">
+        <v>230</v>
+      </c>
+      <c r="J73" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G74" t="s">
+        <v>88</v>
+      </c>
+      <c r="H74" t="s">
         <v>196</v>
       </c>
-      <c r="D64" s="8" t="s">
+      <c r="I74" t="s">
         <v>197</v>
       </c>
-      <c r="E64" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H64" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="I64" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="J64" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B65" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C65" s="7" t="s">
+      <c r="J74" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G75" t="s">
+        <v>88</v>
+      </c>
+      <c r="H75" t="s">
+        <v>231</v>
+      </c>
+      <c r="I75" t="s">
+        <v>232</v>
+      </c>
+      <c r="J75" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G76" t="s">
+        <v>88</v>
+      </c>
+      <c r="H76" t="s">
         <v>198</v>
       </c>
-      <c r="D65" s="7" t="s">
+      <c r="I76" t="s">
         <v>199</v>
       </c>
-      <c r="E65" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="I65" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="J65" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B66" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C66" s="8" t="s">
+      <c r="J76" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G77" t="s">
+        <v>88</v>
+      </c>
+      <c r="H77" t="s">
         <v>200</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="I77" t="s">
         <v>201</v>
       </c>
-      <c r="E66" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H66" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="I66" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="J66" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B67" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C67" s="7" t="s">
+      <c r="J77" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G78" t="s">
+        <v>88</v>
+      </c>
+      <c r="H78" t="s">
         <v>202</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="I78" t="s">
         <v>203</v>
       </c>
-      <c r="E67" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="I67" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="J67" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B68" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C68" s="8" t="s">
+      <c r="J78" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G79" t="s">
+        <v>88</v>
+      </c>
+      <c r="H79" t="s">
         <v>204</v>
       </c>
-      <c r="D68" s="8" t="s">
+      <c r="I79" t="s">
         <v>205</v>
       </c>
-      <c r="E68" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H68" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="I68" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="J68" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B69" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C69" s="7" t="s">
+      <c r="J79" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G80" t="s">
+        <v>88</v>
+      </c>
+      <c r="H80" t="s">
+        <v>233</v>
+      </c>
+      <c r="I80" t="s">
+        <v>234</v>
+      </c>
+      <c r="J80" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="81" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G81" t="s">
+        <v>88</v>
+      </c>
+      <c r="H81" t="s">
         <v>206</v>
       </c>
-      <c r="D69" s="7" t="s">
+      <c r="I81" t="s">
         <v>207</v>
       </c>
-      <c r="E69" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H69" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="I69" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="J69" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B70" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C70" s="8" t="s">
+      <c r="J81" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="82" spans="7:10" x14ac:dyDescent="0.45">
+      <c r="G82" t="s">
+        <v>88</v>
+      </c>
+      <c r="H82" t="s">
         <v>208</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="I82" t="s">
         <v>209</v>
       </c>
-      <c r="E70" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H70" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="I70" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="J70" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="G71" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="I71" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="J71" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="G72" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H72" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="I72" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="J72" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="G73" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H73" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="I73" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="J73" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="G74" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H74" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="I74" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="J74" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="G75" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H75" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="I75" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="J75" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="G76" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H76" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="I76" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="J76" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="G77" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H77" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="I77" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="J77" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="G78" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H78" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="I78" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="J78" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="G79" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="I79" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="G80" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H80" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="I80" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="J80" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="81" spans="7:10" x14ac:dyDescent="0.45">
-      <c r="G81" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H81" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="I81" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="J81" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="82" spans="7:10" x14ac:dyDescent="0.45">
-      <c r="G82" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H82" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="I82" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="J82" s="8" t="s">
-        <v>211</v>
+      <c r="J82" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{364928E4-25E4-4C73-A671-28583CDCDF77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AE6599C-D93D-4FCF-B76F-9DEA4339A369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AE6599C-D93D-4FCF-B76F-9DEA4339A369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{548B6819-3AA6-41E6-AF18-834CEE452DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{548B6819-3AA6-41E6-AF18-834CEE452DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{000BF57F-0B2D-4635-B2DC-A6831C779D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{000BF57F-0B2D-4635-B2DC-A6831C779D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{95197E73-1A20-445A-B37C-BC76F403E4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="260">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -304,6 +304,27 @@
     <t>indesc</t>
   </si>
   <si>
+    <t>en_gas_ccgt,en_gas_turbine,en_gas_chp,en_gas_fuelcell,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_coal_ccs,en_coal_igcc_ccs,en_coal_oxyfuel_ccs,en_nuclear,en_nuclear_smr,en_biomass,en_biomass_cofiring,en_biomass_chp,en_biomass_ccs,en_geothermal</t>
+  </si>
+  <si>
+    <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
+  </si>
+  <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
+    <t>pset_pn</t>
+  </si>
+  <si>
+    <t>-*cofiring*</t>
+  </si>
+  <si>
+    <t>-EFF</t>
+  </si>
+  <si>
+    <t>en_biomass_cofiring*,en_geothermal*</t>
+  </si>
+  <si>
     <t>POL</t>
   </si>
   <si>
@@ -313,9 +334,6 @@
     <t>at grid node - w66161634-220_POL</t>
   </si>
   <si>
-    <t>en_gas_ccgt,en_gas_turbine,en_gas_chp,en_gas_fuelcell,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_coal_ccs,en_coal_igcc_ccs,en_coal_oxyfuel_ccs,en_nuclear,en_nuclear_smr,en_biomass,en_biomass_cofiring,en_biomass_chp,en_biomass_ccs,en_geothermal</t>
-  </si>
-  <si>
     <t>w681264796-400_POL</t>
   </si>
   <si>
@@ -670,9 +688,6 @@
     <t>at grid node - w255284259-400_POL</t>
   </si>
   <si>
-    <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
-  </si>
-  <si>
     <t>w158232924-220_POL</t>
   </si>
   <si>
@@ -749,9 +764,6 @@
   </si>
   <si>
     <t>at grid node - PL58-220_POL</t>
-  </si>
-  <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
     <t>w29098336-220_POL</t>
@@ -1208,1922 +1220,1922 @@
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G11" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" t="s">
+        <v>96</v>
+      </c>
+      <c r="I11" t="s">
+        <v>97</v>
+      </c>
+      <c r="J11" t="s">
+        <v>89</v>
+      </c>
+      <c r="L11" t="s">
+        <v>95</v>
+      </c>
+      <c r="M11" t="s">
+        <v>240</v>
+      </c>
+      <c r="N11" t="s">
+        <v>241</v>
+      </c>
+      <c r="O11" t="s">
         <v>90</v>
-      </c>
-      <c r="E11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G11" t="s">
-        <v>88</v>
-      </c>
-      <c r="H11" t="s">
-        <v>89</v>
-      </c>
-      <c r="I11" t="s">
-        <v>90</v>
-      </c>
-      <c r="J11" t="s">
-        <v>210</v>
-      </c>
-      <c r="L11" t="s">
-        <v>88</v>
-      </c>
-      <c r="M11" t="s">
-        <v>235</v>
-      </c>
-      <c r="N11" t="s">
-        <v>236</v>
-      </c>
-      <c r="O11" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E12" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H12" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I12" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="J12" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L12" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M12" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="N12" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="O12" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E13" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G13" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H13" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I13" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="J13" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L13" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M13" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="N13" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="O13" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H14" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="I14" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="J14" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L14" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M14" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="N14" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="O14" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="I15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J15" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L15" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M15" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="N15" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="O15" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H16" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="I16" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="J16" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L16" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M16" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="N16" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="O16" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H17" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="I17" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="J17" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L17" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M17" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="N17" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="O17" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E18" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H18" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="I18" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="J18" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L18" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M18" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="N18" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="O18" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="I19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J19" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L19" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M19" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="N19" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="O19" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G20" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H20" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="I20" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="J20" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L20" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M20" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="N20" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="O20" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E21" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H21" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="I21" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="J21" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L21" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M21" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="N21" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="O21" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G22" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H22" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I22" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="J22" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L22" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M22" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="N22" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="O22" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C23" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H23" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="I23" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="J23" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L23" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M23" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="N23" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="O23" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E24" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H24" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="I24" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J24" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L24" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M24" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N24" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="O24" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="I25" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="J25" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L25" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M25" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="N25" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="O25" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E26" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G26" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H26" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="I26" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="J26" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="L26" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M26" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="N26" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="O26" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E27" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H27" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="I27" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="J27" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C28" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D28" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E28" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G28" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H28" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="I28" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="J28" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H29" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="I29" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="J29" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="30" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="D30" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E30" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G30" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H30" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="I30" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J30" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="D31" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E31" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H31" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I31" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J31" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="2:15" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C32" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="D32" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E32" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H32" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I32" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="J32" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="D33" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E33" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H33" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I33" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J33" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C34" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="D34" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E34" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H34" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="I34" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="J34" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D35" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E35" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G35" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H35" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I35" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="J35" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="D36" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E36" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H36" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="I36" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="J36" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D37" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E37" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G37" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H37" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="I37" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J37" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C38" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="D38" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E38" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H38" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I38" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J38" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C39" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D39" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E39" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G39" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H39" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I39" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="J39" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C40" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D40" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E40" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G40" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H40" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="I40" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="J40" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C41" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D41" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E41" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G41" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H41" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="I41" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="J41" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D42" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E42" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G42" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H42" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="I42" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="J42" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C43" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D43" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E43" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G43" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H43" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="I43" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="J43" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C44" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="D44" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E44" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G44" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H44" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I44" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="J44" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C45" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="D45" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E45" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H45" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="I45" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="J45" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C46" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D46" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E46" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H46" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="I46" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="J46" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C47" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="D47" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E47" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G47" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H47" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="I47" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="J47" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C48" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D48" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E48" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G48" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H48" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="I48" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="J48" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C49" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="D49" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E49" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G49" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H49" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="I49" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="J49" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C50" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D50" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E50" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G50" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H50" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="I50" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="J50" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C51" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="D51" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E51" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G51" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H51" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="I51" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="J51" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C52" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="D52" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E52" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G52" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H52" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="I52" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="J52" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C53" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="D53" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E53" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G53" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H53" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="I53" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="J53" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C54" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D54" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E54" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G54" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H54" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="I54" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="J54" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C55" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D55" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E55" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G55" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H55" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="I55" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="J55" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C56" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="D56" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E56" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G56" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H56" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="I56" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="J56" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C57" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D57" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E57" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G57" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H57" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="I57" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="J57" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C58" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D58" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E58" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G58" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H58" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="I58" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="J58" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C59" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D59" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E59" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G59" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H59" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="I59" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="J59" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C60" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D60" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="E60" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G60" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H60" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I60" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="J60" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C61" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D61" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E61" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G61" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H61" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="I61" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="J61" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C62" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="D62" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E62" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G62" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H62" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="I62" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="J62" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C63" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="D63" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E63" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G63" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H63" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="I63" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="J63" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C64" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="D64" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E64" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G64" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H64" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="I64" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="J64" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C65" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="D65" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E65" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G65" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H65" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="I65" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="J65" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C66" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D66" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E66" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G66" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H66" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="I66" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="J66" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C67" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="D67" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E67" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G67" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H67" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="I67" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="J67" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C68" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D68" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E68" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G68" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H68" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="I68" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="J68" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="69" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C69" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D69" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E69" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G69" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H69" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="I69" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="J69" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="70" spans="2:10" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C70" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="D70" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E70" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="G70" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H70" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="I70" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="J70" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="71" spans="2:10" x14ac:dyDescent="0.45">
       <c r="G71" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H71" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="I71" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="J71" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.45">
       <c r="G72" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H72" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="I72" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="J72" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.45">
       <c r="G73" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H73" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="I73" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="J73" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.45">
       <c r="G74" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H74" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="I74" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="J74" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.45">
       <c r="G75" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H75" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="I75" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="J75" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.45">
       <c r="G76" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H76" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="I76" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="J76" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.45">
       <c r="G77" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H77" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="I77" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="J77" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.45">
       <c r="G78" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H78" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="I78" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J78" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.45">
       <c r="G79" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H79" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="I79" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J79" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.45">
       <c r="G80" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H80" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="I80" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="J80" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="81" spans="7:10" x14ac:dyDescent="0.45">
       <c r="G81" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H81" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="I81" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="J81" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
     <row r="82" spans="7:10" x14ac:dyDescent="0.45">
       <c r="G82" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H82" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="I82" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="J82" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -4349,6 +4361,9 @@
       <c r="G28" t="s">
         <v>5</v>
       </c>
+      <c r="H28" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C29" t="s">
@@ -4371,6 +4386,9 @@
       <c r="G30" s="1">
         <v>1</v>
       </c>
+      <c r="H30" s="3" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="31" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C31" t="s">
@@ -4528,6 +4546,9 @@
         <v>66</v>
       </c>
       <c r="F49" t="s">
+        <v>91</v>
+      </c>
+      <c r="G49" t="s">
         <v>65</v>
       </c>
     </row>
@@ -4541,7 +4562,10 @@
       <c r="E50" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F50" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G50" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4555,8 +4579,19 @@
       <c r="E51" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F51" t="s">
+      <c r="G51" t="s">
         <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C52" t="s">
+        <v>64</v>
+      </c>
+      <c r="D52">
+        <v>2100</v>
+      </c>
+      <c r="F52" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.45">
